--- a/data/exports/optimization/lotto_genetic_optimizer_results.xlsx
+++ b/data/exports/optimization/lotto_genetic_optimizer_results.xlsx
@@ -532,7 +532,7 @@
         <v>49</v>
       </c>
       <c r="H2" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="I2" t="n">
         <v>156</v>
@@ -556,7 +556,7 @@
         <v>13.3207</v>
       </c>
       <c r="P2" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -565,7 +565,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -592,7 +592,7 @@
         <v>49</v>
       </c>
       <c r="H3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I3" t="n">
         <v>156</v>
@@ -616,7 +616,7 @@
         <v>13.3207</v>
       </c>
       <c r="P3" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -625,7 +625,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
         <v>49</v>
       </c>
       <c r="H4" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
         <v>156</v>
@@ -676,7 +676,7 @@
         <v>13.3207</v>
       </c>
       <c r="P4" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -685,7 +685,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -712,7 +712,7 @@
         <v>49</v>
       </c>
       <c r="H5" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="I5" t="n">
         <v>156</v>
@@ -736,7 +736,7 @@
         <v>13.3207</v>
       </c>
       <c r="P5" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -772,7 +772,7 @@
         <v>49</v>
       </c>
       <c r="H6" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="I6" t="n">
         <v>156</v>
@@ -796,7 +796,7 @@
         <v>13.3207</v>
       </c>
       <c r="P6" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
         <v>49</v>
       </c>
       <c r="H7" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I7" t="n">
         <v>156</v>
@@ -856,7 +856,7 @@
         <v>13.3207</v>
       </c>
       <c r="P7" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
         <v>49</v>
       </c>
       <c r="H8" t="n">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="I8" t="n">
         <v>156</v>
@@ -916,7 +916,7 @@
         <v>13.3207</v>
       </c>
       <c r="P8" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
         <v>49</v>
       </c>
       <c r="H9" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="I9" t="n">
         <v>156</v>
@@ -976,7 +976,7 @@
         <v>13.3207</v>
       </c>
       <c r="P9" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
         <v>49</v>
       </c>
       <c r="H10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I10" t="n">
         <v>156</v>
@@ -1036,7 +1036,7 @@
         <v>13.3207</v>
       </c>
       <c r="P10" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
         <v>49</v>
       </c>
       <c r="H11" t="n">
-        <v>19</v>
+        <v>58</v>
       </c>
       <c r="I11" t="n">
         <v>156</v>
@@ -1096,7 +1096,7 @@
         <v>13.3207</v>
       </c>
       <c r="P11" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
         <v>49</v>
       </c>
       <c r="H12" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="I12" t="n">
         <v>156</v>
@@ -1156,7 +1156,7 @@
         <v>13.3207</v>
       </c>
       <c r="P12" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1192,7 @@
         <v>49</v>
       </c>
       <c r="H13" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="I13" t="n">
         <v>156</v>
@@ -1216,7 +1216,7 @@
         <v>13.3207</v>
       </c>
       <c r="P13" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
         <v>49</v>
       </c>
       <c r="H14" t="n">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="I14" t="n">
         <v>156</v>
@@ -1276,7 +1276,7 @@
         <v>13.3207</v>
       </c>
       <c r="P14" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1312,7 @@
         <v>49</v>
       </c>
       <c r="H15" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="I15" t="n">
         <v>156</v>
@@ -1336,7 +1336,7 @@
         <v>13.3207</v>
       </c>
       <c r="P15" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
         <v>49</v>
       </c>
       <c r="H16" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I16" t="n">
         <v>156</v>
@@ -1396,7 +1396,7 @@
         <v>13.3207</v>
       </c>
       <c r="P16" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
         <v>49</v>
       </c>
       <c r="H17" t="n">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="I17" t="n">
         <v>156</v>
@@ -1456,7 +1456,7 @@
         <v>13.3207</v>
       </c>
       <c r="P17" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1492,7 @@
         <v>49</v>
       </c>
       <c r="H18" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I18" t="n">
         <v>156</v>
@@ -1516,7 +1516,7 @@
         <v>13.3207</v>
       </c>
       <c r="P18" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1552,7 @@
         <v>49</v>
       </c>
       <c r="H19" t="n">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="I19" t="n">
         <v>156</v>
@@ -1576,7 +1576,7 @@
         <v>13.3207</v>
       </c>
       <c r="P19" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
         <v>49</v>
       </c>
       <c r="H20" t="n">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="I20" t="n">
         <v>156</v>
@@ -1636,7 +1636,7 @@
         <v>13.3207</v>
       </c>
       <c r="P20" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
         <v>49</v>
       </c>
       <c r="H21" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="I21" t="n">
         <v>156</v>
@@ -1696,7 +1696,7 @@
         <v>13.3207</v>
       </c>
       <c r="P21" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
         <v>49</v>
       </c>
       <c r="H22" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="I22" t="n">
         <v>156</v>
@@ -1756,7 +1756,7 @@
         <v>13.3207</v>
       </c>
       <c r="P22" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -1792,7 +1792,7 @@
         <v>49</v>
       </c>
       <c r="H23" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="I23" t="n">
         <v>156</v>
@@ -1816,7 +1816,7 @@
         <v>13.3207</v>
       </c>
       <c r="P23" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -1852,7 +1852,7 @@
         <v>49</v>
       </c>
       <c r="H24" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="I24" t="n">
         <v>156</v>
@@ -1876,7 +1876,7 @@
         <v>13.3207</v>
       </c>
       <c r="P24" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
         <v>49</v>
       </c>
       <c r="H25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I25" t="n">
         <v>156</v>
@@ -1936,7 +1936,7 @@
         <v>13.3207</v>
       </c>
       <c r="P25" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -1972,7 +1972,7 @@
         <v>49</v>
       </c>
       <c r="H26" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I26" t="n">
         <v>156</v>
@@ -1996,7 +1996,7 @@
         <v>13.3207</v>
       </c>
       <c r="P26" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2032,7 @@
         <v>49</v>
       </c>
       <c r="H27" t="n">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="I27" t="n">
         <v>156</v>
@@ -2056,7 +2056,7 @@
         <v>13.3207</v>
       </c>
       <c r="P27" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
         <v>49</v>
       </c>
       <c r="H28" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="I28" t="n">
         <v>156</v>
@@ -2116,7 +2116,7 @@
         <v>13.3207</v>
       </c>
       <c r="P28" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -2152,7 +2152,7 @@
         <v>49</v>
       </c>
       <c r="H29" t="n">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="I29" t="n">
         <v>156</v>
@@ -2176,7 +2176,7 @@
         <v>13.3207</v>
       </c>
       <c r="P29" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
         <v>49</v>
       </c>
       <c r="H30" t="n">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="I30" t="n">
         <v>156</v>
@@ -2236,7 +2236,7 @@
         <v>13.3207</v>
       </c>
       <c r="P30" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2272,7 @@
         <v>49</v>
       </c>
       <c r="H31" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="I31" t="n">
         <v>156</v>
@@ -2296,7 +2296,7 @@
         <v>13.3207</v>
       </c>
       <c r="P31" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -2314,7 +2314,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C32" t="n">
         <v>6</v>
@@ -2332,10 +2332,10 @@
         <v>49</v>
       </c>
       <c r="H32" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="I32" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J32" t="n">
         <v>3</v>
@@ -2344,19 +2344,19 @@
         <v>3</v>
       </c>
       <c r="L32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N32" t="n">
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>13.2454</v>
+        <v>13.3207</v>
       </c>
       <c r="P32" t="n">
-        <v>538.1334000000001</v>
+        <v>540.9817</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -2374,13 +2374,13 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D33" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E33" t="n">
         <v>44</v>
@@ -2392,10 +2392,10 @@
         <v>49</v>
       </c>
       <c r="H33" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I33" t="n">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="J33" t="n">
         <v>3</v>
@@ -2413,10 +2413,10 @@
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>12.2082</v>
+        <v>13.2454</v>
       </c>
       <c r="P33" t="n">
-        <v>537.4805</v>
+        <v>538.6134</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
@@ -2425,7 +2425,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -2434,49 +2434,49 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C34" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D34" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E34" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="F34" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G34" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H34" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="I34" t="n">
-        <v>118</v>
+        <v>165</v>
       </c>
       <c r="J34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>12.0167</v>
+        <v>12.2082</v>
       </c>
       <c r="P34" t="n">
-        <v>537.0816</v>
+        <v>537.9605</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -2494,7 +2494,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C35" t="n">
         <v>6</v>
@@ -2503,25 +2503,25 @@
         <v>8</v>
       </c>
       <c r="E35" t="n">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="F35" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G35" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H35" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I35" t="n">
-        <v>158</v>
+        <v>118</v>
       </c>
       <c r="J35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L35" t="n">
         <v>2</v>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>13.5056</v>
+        <v>12.0167</v>
       </c>
       <c r="P35" t="n">
-        <v>536.6439</v>
+        <v>537.4216</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -2554,13 +2554,13 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C36" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D36" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E36" t="n">
         <v>44</v>
@@ -2572,10 +2572,10 @@
         <v>49</v>
       </c>
       <c r="H36" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="I36" t="n">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J36" t="n">
         <v>3</v>
@@ -2584,19 +2584,19 @@
         <v>3</v>
       </c>
       <c r="L36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N36" t="n">
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>11.876</v>
+        <v>13.5056</v>
       </c>
       <c r="P36" t="n">
-        <v>536.0701</v>
+        <v>537.1239</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -2617,25 +2617,25 @@
         <v>2</v>
       </c>
       <c r="C37" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D37" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E37" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F37" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G37" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H37" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="I37" t="n">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="J37" t="n">
         <v>3</v>
@@ -2644,19 +2644,19 @@
         <v>3</v>
       </c>
       <c r="L37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>13.0384</v>
+        <v>11.876</v>
       </c>
       <c r="P37" t="n">
-        <v>535.276</v>
+        <v>536.5501</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
         <v>47</v>
       </c>
       <c r="H38" t="n">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="I38" t="n">
         <v>150</v>
@@ -2716,7 +2716,7 @@
         <v>13.0384</v>
       </c>
       <c r="P38" t="n">
-        <v>535.276</v>
+        <v>535.616</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -2743,16 +2743,16 @@
         <v>8</v>
       </c>
       <c r="E39" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F39" t="n">
         <v>44</v>
       </c>
       <c r="G39" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H39" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I39" t="n">
         <v>150</v>
@@ -2770,13 +2770,13 @@
         <v>4</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O39" t="n">
-        <v>11.8423</v>
+        <v>13.0384</v>
       </c>
       <c r="P39" t="n">
-        <v>535.1057</v>
+        <v>535.616</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -2803,25 +2803,25 @@
         <v>8</v>
       </c>
       <c r="E40" t="n">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="F40" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G40" t="n">
         <v>49</v>
       </c>
       <c r="H40" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="I40" t="n">
-        <v>126</v>
+        <v>150</v>
       </c>
       <c r="J40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L40" t="n">
         <v>2</v>
@@ -2833,10 +2833,10 @@
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>11.8929</v>
+        <v>11.8423</v>
       </c>
       <c r="P40" t="n">
-        <v>533.5521</v>
+        <v>535.4057</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -2854,16 +2854,16 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C41" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D41" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E41" t="n">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="F41" t="n">
         <v>47</v>
@@ -2872,31 +2872,31 @@
         <v>49</v>
       </c>
       <c r="H41" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I41" t="n">
-        <v>149</v>
+        <v>126</v>
       </c>
       <c r="J41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>14.2352</v>
+        <v>11.8929</v>
       </c>
       <c r="P41" t="n">
-        <v>532.8079</v>
+        <v>534.0321</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -2914,13 +2914,13 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D42" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E42" t="n">
         <v>44</v>
@@ -2932,10 +2932,10 @@
         <v>49</v>
       </c>
       <c r="H42" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="I42" t="n">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="J42" t="n">
         <v>3</v>
@@ -2944,19 +2944,19 @@
         <v>3</v>
       </c>
       <c r="L42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O42" t="n">
-        <v>12.3871</v>
+        <v>14.2352</v>
       </c>
       <c r="P42" t="n">
-        <v>532.2077</v>
+        <v>533.1479</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -2980,28 +2980,28 @@
         <v>8</v>
       </c>
       <c r="D43" t="n">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="E43" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F43" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G43" t="n">
         <v>49</v>
       </c>
       <c r="H43" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="I43" t="n">
-        <v>198</v>
+        <v>160</v>
       </c>
       <c r="J43" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L43" t="n">
         <v>2</v>
@@ -3010,13 +3010,13 @@
         <v>4</v>
       </c>
       <c r="N43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>13.4253</v>
+        <v>12.3871</v>
       </c>
       <c r="P43" t="n">
-        <v>532.0834</v>
+        <v>532.6876999999999</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -3037,31 +3037,31 @@
         <v>2</v>
       </c>
       <c r="C44" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D44" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E44" t="n">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="F44" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G44" t="n">
         <v>49</v>
       </c>
       <c r="H44" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="I44" t="n">
-        <v>118</v>
+        <v>198</v>
       </c>
       <c r="J44" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K44" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L44" t="n">
         <v>2</v>
@@ -3070,13 +3070,13 @@
         <v>4</v>
       </c>
       <c r="N44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O44" t="n">
-        <v>12.8779</v>
+        <v>13.4253</v>
       </c>
       <c r="P44" t="n">
-        <v>531.7147</v>
+        <v>532.5634</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
@@ -3085,7 +3085,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
         <v>49</v>
       </c>
       <c r="H45" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I45" t="n">
         <v>193</v>
@@ -3136,7 +3136,7 @@
         <v>14.3332</v>
       </c>
       <c r="P45" t="n">
-        <v>531.5729</v>
+        <v>532.0929</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -3163,19 +3163,19 @@
         <v>8</v>
       </c>
       <c r="E46" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="F46" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G46" t="n">
         <v>49</v>
       </c>
       <c r="H46" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I46" t="n">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="J46" t="n">
         <v>2</v>
@@ -3184,19 +3184,19 @@
         <v>4</v>
       </c>
       <c r="L46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M46" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O46" t="n">
-        <v>8.2849</v>
+        <v>12.8779</v>
       </c>
       <c r="P46" t="n">
-        <v>530.1323</v>
+        <v>532.0146999999999</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -3220,43 +3220,43 @@
         <v>6</v>
       </c>
       <c r="D47" t="n">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="E47" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F47" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G47" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H47" t="n">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="I47" t="n">
-        <v>149</v>
+        <v>187</v>
       </c>
       <c r="J47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M47" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>12.522</v>
+        <v>11.8423</v>
       </c>
       <c r="P47" t="n">
-        <v>528.785</v>
+        <v>531.1657</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -3274,16 +3274,16 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C48" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D48" t="n">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E48" t="n">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="F48" t="n">
         <v>47</v>
@@ -3292,16 +3292,16 @@
         <v>49</v>
       </c>
       <c r="H48" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I48" t="n">
-        <v>187</v>
+        <v>139</v>
       </c>
       <c r="J48" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K48" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L48" t="n">
         <v>3</v>
@@ -3313,10 +3313,10 @@
         <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>8.867900000000001</v>
+        <v>8.2849</v>
       </c>
       <c r="P48" t="n">
-        <v>528.3498</v>
+        <v>530.7123</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -3334,49 +3334,49 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C49" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D49" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="E49" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="F49" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G49" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H49" t="n">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="I49" t="n">
-        <v>140</v>
+        <v>187</v>
       </c>
       <c r="J49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M49" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>8.6023</v>
+        <v>8.867900000000001</v>
       </c>
       <c r="P49" t="n">
-        <v>528.3258</v>
+        <v>529.1898</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -3403,19 +3403,19 @@
         <v>8</v>
       </c>
       <c r="E50" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F50" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G50" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H50" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="I50" t="n">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="J50" t="n">
         <v>3</v>
@@ -3430,13 +3430,13 @@
         <v>5</v>
       </c>
       <c r="N50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>13.4373</v>
+        <v>12.522</v>
       </c>
       <c r="P50" t="n">
-        <v>527.0132</v>
+        <v>529.125</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -3457,46 +3457,46 @@
         <v>2</v>
       </c>
       <c r="C51" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D51" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="E51" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="F51" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G51" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H51" t="n">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="I51" t="n">
-        <v>185</v>
+        <v>140</v>
       </c>
       <c r="J51" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N51" t="n">
         <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>9.134499999999999</v>
+        <v>8.6023</v>
       </c>
       <c r="P51" t="n">
-        <v>525.7963999999999</v>
+        <v>528.9858</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -3523,40 +3523,40 @@
         <v>8</v>
       </c>
       <c r="E52" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="F52" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G52" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H52" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="I52" t="n">
-        <v>136</v>
+        <v>155</v>
       </c>
       <c r="J52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K52" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M52" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O52" t="n">
-        <v>7.6158</v>
+        <v>13.4373</v>
       </c>
       <c r="P52" t="n">
-        <v>525.3394</v>
+        <v>527.3532</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -3577,46 +3577,46 @@
         <v>2</v>
       </c>
       <c r="C53" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D53" t="n">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="E53" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F53" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G53" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H53" t="n">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="I53" t="n">
-        <v>147</v>
+        <v>185</v>
       </c>
       <c r="J53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M53" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N53" t="n">
         <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>11.5239</v>
+        <v>9.134499999999999</v>
       </c>
       <c r="P53" t="n">
-        <v>525.2696999999999</v>
+        <v>526.2764</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -3637,46 +3637,46 @@
         <v>2</v>
       </c>
       <c r="C54" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D54" t="n">
+        <v>8</v>
+      </c>
+      <c r="E54" t="n">
         <v>29</v>
       </c>
-      <c r="E54" t="n">
-        <v>44</v>
-      </c>
       <c r="F54" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G54" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H54" t="n">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="I54" t="n">
-        <v>179</v>
+        <v>136</v>
       </c>
       <c r="J54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N54" t="n">
         <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>7.3919</v>
+        <v>7.6158</v>
       </c>
       <c r="P54" t="n">
-        <v>524.0397</v>
+        <v>525.6794</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -3697,46 +3697,46 @@
         <v>2</v>
       </c>
       <c r="C55" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D55" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="E55" t="n">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="F55" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G55" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H55" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="I55" t="n">
-        <v>119</v>
+        <v>179</v>
       </c>
       <c r="J55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K55" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M55" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N55" t="n">
         <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>11.5239</v>
+        <v>7.3919</v>
       </c>
       <c r="P55" t="n">
-        <v>521.7696999999999</v>
+        <v>524.5196999999999</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
@@ -3745,7 +3745,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3763,7 @@
         <v>8</v>
       </c>
       <c r="E56" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F56" t="n">
         <v>44</v>
@@ -3772,10 +3772,10 @@
         <v>47</v>
       </c>
       <c r="H56" t="n">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="I56" t="n">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="J56" t="n">
         <v>2</v>
@@ -3784,19 +3784,19 @@
         <v>4</v>
       </c>
       <c r="L56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M56" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N56" t="n">
         <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>8.025</v>
+        <v>11.5239</v>
       </c>
       <c r="P56" t="n">
-        <v>521.0824</v>
+        <v>522.1097</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -3832,7 +3832,7 @@
         <v>49</v>
       </c>
       <c r="H57" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I57" t="n">
         <v>125</v>
@@ -3856,7 +3856,7 @@
         <v>9.499499999999999</v>
       </c>
       <c r="P57" t="n">
-        <v>520.9887</v>
+        <v>521.2886999999999</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -3892,7 +3892,7 @@
         <v>49</v>
       </c>
       <c r="H58" t="n">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="I58" t="n">
         <v>179</v>
@@ -3916,7 +3916,7 @@
         <v>7.7097</v>
       </c>
       <c r="P58" t="n">
-        <v>519.5343</v>
+        <v>520.0143</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -3976,7 +3976,7 @@
         <v>8.294600000000001</v>
       </c>
       <c r="P59" t="n">
-        <v>514.8164</v>
+        <v>515.1564</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -4012,7 +4012,7 @@
         <v>49</v>
       </c>
       <c r="H60" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I60" t="n">
         <v>152</v>
@@ -4036,7 +4036,7 @@
         <v>14.3052</v>
       </c>
       <c r="P60" t="n">
-        <v>514.5631</v>
+        <v>514.9031</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -4072,7 +4072,7 @@
         <v>47</v>
       </c>
       <c r="H61" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I61" t="n">
         <v>112</v>
@@ -4096,7 +4096,7 @@
         <v>13.5204</v>
       </c>
       <c r="P61" t="n">
-        <v>510.4009</v>
+        <v>510.7409</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
@@ -4105,7 +4105,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -4156,7 +4156,7 @@
         <v>10.6132</v>
       </c>
       <c r="P62" t="n">
-        <v>509.053</v>
+        <v>509.533</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -4165,7 +4165,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -4180,11 +4180,11 @@
         <v>6</v>
       </c>
       <c r="D63" t="n">
+        <v>8</v>
+      </c>
+      <c r="E63" t="n">
         <v>36</v>
       </c>
-      <c r="E63" t="n">
-        <v>44</v>
-      </c>
       <c r="F63" t="n">
         <v>47</v>
       </c>
@@ -4192,16 +4192,16 @@
         <v>49</v>
       </c>
       <c r="H63" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="I63" t="n">
-        <v>184</v>
+        <v>148</v>
       </c>
       <c r="J63" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L63" t="n">
         <v>2</v>
@@ -4213,10 +4213,10 @@
         <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>10.4995</v>
+        <v>9.8712</v>
       </c>
       <c r="P63" t="n">
-        <v>502.8888</v>
+        <v>505.4779</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
@@ -4225,7 +4225,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -4237,10 +4237,10 @@
         <v>2</v>
       </c>
       <c r="C64" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D64" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E64" t="n">
         <v>44</v>
@@ -4252,10 +4252,10 @@
         <v>49</v>
       </c>
       <c r="H64" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="I64" t="n">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="J64" t="n">
         <v>4</v>
@@ -4264,19 +4264,19 @@
         <v>2</v>
       </c>
       <c r="L64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N64" t="n">
         <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>7.8128</v>
+        <v>10.4995</v>
       </c>
       <c r="P64" t="n">
-        <v>501.672</v>
+        <v>503.2288</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -4297,46 +4297,46 @@
         <v>2</v>
       </c>
       <c r="C65" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D65" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="E65" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="F65" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G65" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H65" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I65" t="n">
-        <v>132</v>
+        <v>181</v>
       </c>
       <c r="J65" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K65" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M65" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N65" t="n">
         <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>7.4027</v>
+        <v>7.8128</v>
       </c>
       <c r="P65" t="n">
-        <v>498.2068</v>
+        <v>502.152</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -4357,46 +4357,46 @@
         <v>2</v>
       </c>
       <c r="C66" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D66" t="n">
+        <v>8</v>
+      </c>
+      <c r="E66" t="n">
         <v>25</v>
       </c>
-      <c r="E66" t="n">
-        <v>44</v>
-      </c>
       <c r="F66" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G66" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H66" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="I66" t="n">
-        <v>175</v>
+        <v>132</v>
       </c>
       <c r="J66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N66" t="n">
         <v>0</v>
       </c>
       <c r="O66" t="n">
-        <v>7.1722</v>
+        <v>7.4027</v>
       </c>
       <c r="P66" t="n">
-        <v>497.2904</v>
+        <v>498.5468</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
@@ -4405,7 +4405,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -4417,25 +4417,25 @@
         <v>2</v>
       </c>
       <c r="C67" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D67" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E67" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F67" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G67" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H67" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I67" t="n">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="J67" t="n">
         <v>3</v>
@@ -4444,19 +4444,19 @@
         <v>3</v>
       </c>
       <c r="L67" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M67" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
-        <v>14.7323</v>
+        <v>7.1722</v>
       </c>
       <c r="P67" t="n">
-        <v>496.0307</v>
+        <v>497.7704</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -4483,19 +4483,19 @@
         <v>8</v>
       </c>
       <c r="E68" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F68" t="n">
         <v>49</v>
       </c>
       <c r="G68" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H68" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="I68" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="J68" t="n">
         <v>3</v>
@@ -4510,13 +4510,13 @@
         <v>4</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O68" t="n">
-        <v>13.1514</v>
+        <v>14.7323</v>
       </c>
       <c r="P68" t="n">
-        <v>492.2786</v>
+        <v>496.5107</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
@@ -4525,7 +4525,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -4540,10 +4540,10 @@
         <v>6</v>
       </c>
       <c r="D69" t="n">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="E69" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F69" t="n">
         <v>49</v>
@@ -4552,31 +4552,31 @@
         <v>51</v>
       </c>
       <c r="H69" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="I69" t="n">
-        <v>199</v>
+        <v>160</v>
       </c>
       <c r="J69" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L69" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M69" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N69" t="n">
         <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>14.1195</v>
+        <v>13.1514</v>
       </c>
       <c r="P69" t="n">
-        <v>489.8787</v>
+        <v>492.4786</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -4585,7 +4585,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -4600,43 +4600,43 @@
         <v>6</v>
       </c>
       <c r="D70" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E70" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F70" t="n">
         <v>49</v>
       </c>
       <c r="G70" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H70" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I70" t="n">
-        <v>159</v>
+        <v>199</v>
       </c>
       <c r="J70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L70" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M70" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
-        <v>13.2755</v>
+        <v>14.1195</v>
       </c>
       <c r="P70" t="n">
-        <v>482.5289</v>
+        <v>490.2187</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
         <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C71" t="n">
         <v>8</v>
@@ -4669,13 +4669,13 @@
         <v>49</v>
       </c>
       <c r="G71" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H71" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I71" t="n">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="J71" t="n">
         <v>4</v>
@@ -4693,10 +4693,10 @@
         <v>0</v>
       </c>
       <c r="O71" t="n">
-        <v>12.9677</v>
+        <v>13.1818</v>
       </c>
       <c r="P71" t="n">
-        <v>457.4991</v>
+        <v>458.2145</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -4717,46 +4717,46 @@
         <v>2</v>
       </c>
       <c r="C72" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D72" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E72" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F72" t="n">
         <v>49</v>
       </c>
       <c r="G72" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H72" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I72" t="n">
-        <v>164</v>
+        <v>203</v>
       </c>
       <c r="J72" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K72" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M72" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N72" t="n">
         <v>0</v>
       </c>
       <c r="O72" t="n">
-        <v>12.7687</v>
+        <v>12.9677</v>
       </c>
       <c r="P72" t="n">
-        <v>457.2818</v>
+        <v>458.1591</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -4780,28 +4780,28 @@
         <v>6</v>
       </c>
       <c r="D73" t="n">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="E73" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F73" t="n">
         <v>49</v>
       </c>
       <c r="G73" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H73" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="I73" t="n">
-        <v>204</v>
+        <v>164</v>
       </c>
       <c r="J73" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L73" t="n">
         <v>2</v>
@@ -4813,10 +4813,10 @@
         <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>13.7026</v>
+        <v>12.7687</v>
       </c>
       <c r="P73" t="n">
-        <v>456.3364</v>
+        <v>457.4818</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4852,7 @@
         <v>54</v>
       </c>
       <c r="H74" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I74" t="n">
         <v>204</v>
@@ -4876,7 +4876,7 @@
         <v>12.8779</v>
       </c>
       <c r="P74" t="n">
-        <v>456.3147</v>
+        <v>456.7947</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -4900,43 +4900,43 @@
         <v>6</v>
       </c>
       <c r="D75" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E75" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F75" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G75" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H75" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="I75" t="n">
-        <v>161</v>
+        <v>204</v>
       </c>
       <c r="J75" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M75" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N75" t="n">
         <v>0</v>
       </c>
       <c r="O75" t="n">
-        <v>12.9089</v>
+        <v>13.7026</v>
       </c>
       <c r="P75" t="n">
-        <v>446.5723</v>
+        <v>456.6764</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4972,7 @@
         <v>54</v>
       </c>
       <c r="H76" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="I76" t="n">
         <v>161</v>
@@ -4996,7 +4996,7 @@
         <v>12.9089</v>
       </c>
       <c r="P76" t="n">
-        <v>446.5723</v>
+        <v>446.9123</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -5005,7 +5005,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>2026-05-23 08:32:37</t>
+          <t>2026-05-24 05:36:48</t>
         </is>
       </c>
     </row>
@@ -5045,10 +5045,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>518.5201</v>
+        <v>518.9601</v>
       </c>
       <c r="C2" t="n">
-        <v>438.884</v>
+        <v>439.0952</v>
       </c>
     </row>
     <row r="3">
@@ -5056,10 +5056,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>525.6767</v>
+        <v>524.3188</v>
       </c>
       <c r="C3" t="n">
-        <v>500.6946</v>
+        <v>500.2401</v>
       </c>
     </row>
     <row r="4">
@@ -5067,10 +5067,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>533.9547</v>
+        <v>529.0447</v>
       </c>
       <c r="C4" t="n">
-        <v>508.1856</v>
+        <v>506.6022</v>
       </c>
     </row>
     <row r="5">
@@ -5078,10 +5078,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>536.2007</v>
+        <v>540.3200000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>513.0381</v>
+        <v>512.8799</v>
       </c>
     </row>
     <row r="6">
@@ -5089,10 +5089,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>539.3248</v>
+        <v>540.3200000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>518.4118</v>
+        <v>518.1374</v>
       </c>
     </row>
     <row r="7">
@@ -5100,10 +5100,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>540.5017</v>
+        <v>540.3200000000001</v>
       </c>
       <c r="C7" t="n">
-        <v>524.2001</v>
+        <v>521.7063000000001</v>
       </c>
     </row>
     <row r="8">
@@ -5111,10 +5111,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="C8" t="n">
-        <v>529.9435</v>
+        <v>525.8828999999999</v>
       </c>
     </row>
     <row r="9">
@@ -5122,10 +5122,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="C9" t="n">
-        <v>532.876</v>
+        <v>529.317</v>
       </c>
     </row>
     <row r="10">
@@ -5133,10 +5133,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="C10" t="n">
-        <v>533.3593</v>
+        <v>531.9712</v>
       </c>
     </row>
     <row r="11">
@@ -5144,10 +5144,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="C11" t="n">
-        <v>536.419</v>
+        <v>536.4147</v>
       </c>
     </row>
     <row r="12">
@@ -5155,10 +5155,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="C12" t="n">
-        <v>536.1007</v>
+        <v>536.096</v>
       </c>
     </row>
     <row r="13">
@@ -5166,10 +5166,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="C13" t="n">
-        <v>534.9971</v>
+        <v>535.7974</v>
       </c>
     </row>
     <row r="14">
@@ -5177,10 +5177,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="C14" t="n">
-        <v>536.0697</v>
+        <v>536.5204</v>
       </c>
     </row>
     <row r="15">
@@ -5188,10 +5188,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="C15" t="n">
-        <v>537.6972</v>
+        <v>538.2291</v>
       </c>
     </row>
     <row r="16">
@@ -5199,10 +5199,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="C16" t="n">
-        <v>537.875</v>
+        <v>538.3438</v>
       </c>
     </row>
     <row r="17">
@@ -5210,10 +5210,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="C17" t="n">
-        <v>535.5089</v>
+        <v>535.6775</v>
       </c>
     </row>
     <row r="18">
@@ -5221,10 +5221,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="C18" t="n">
-        <v>537.345</v>
+        <v>538.1394</v>
       </c>
     </row>
     <row r="19">
@@ -5232,10 +5232,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="C19" t="n">
-        <v>537.1387</v>
+        <v>537.475</v>
       </c>
     </row>
     <row r="20">
@@ -5243,10 +5243,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="C20" t="n">
-        <v>535.7399</v>
+        <v>535.9163</v>
       </c>
     </row>
     <row r="21">
@@ -5254,10 +5254,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="C21" t="n">
-        <v>535.6478</v>
+        <v>536.3330999999999</v>
       </c>
     </row>
     <row r="22">
@@ -5265,10 +5265,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="C22" t="n">
-        <v>536.7597</v>
+        <v>537.3239</v>
       </c>
     </row>
     <row r="23">
@@ -5276,10 +5276,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="C23" t="n">
-        <v>536.7083</v>
+        <v>536.9828</v>
       </c>
     </row>
     <row r="24">
@@ -5287,10 +5287,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="C24" t="n">
-        <v>536.9880000000001</v>
+        <v>537.4806</v>
       </c>
     </row>
     <row r="25">
@@ -5298,10 +5298,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="C25" t="n">
-        <v>537.1462</v>
+        <v>537.7269</v>
       </c>
     </row>
     <row r="26">
@@ -5309,10 +5309,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="C26" t="n">
-        <v>537.2184</v>
+        <v>537.9197</v>
       </c>
     </row>
     <row r="27">
@@ -5320,10 +5320,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="C27" t="n">
-        <v>536.1341</v>
+        <v>536.4245</v>
       </c>
     </row>
     <row r="28">
@@ -5331,10 +5331,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="C28" t="n">
-        <v>536.0535</v>
+        <v>536.6409</v>
       </c>
     </row>
     <row r="29">
@@ -5342,10 +5342,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="C29" t="n">
-        <v>536.3962</v>
+        <v>536.2771</v>
       </c>
     </row>
     <row r="30">
@@ -5353,10 +5353,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="C30" t="n">
-        <v>536.8715999999999</v>
+        <v>537.9097</v>
       </c>
     </row>
     <row r="31">
@@ -5364,10 +5364,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="C31" t="n">
-        <v>536.6851</v>
+        <v>537.1289</v>
       </c>
     </row>
     <row r="32">
@@ -5375,10 +5375,10 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="C32" t="n">
-        <v>537.255</v>
+        <v>537.7095</v>
       </c>
     </row>
     <row r="33">
@@ -5386,10 +5386,10 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="C33" t="n">
-        <v>535.274</v>
+        <v>535.6396</v>
       </c>
     </row>
     <row r="34">
@@ -5397,10 +5397,10 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="C34" t="n">
-        <v>536.0551</v>
+        <v>536.7017</v>
       </c>
     </row>
     <row r="35">
@@ -5408,10 +5408,10 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="C35" t="n">
-        <v>536.1119</v>
+        <v>536.4136999999999</v>
       </c>
     </row>
     <row r="36">
@@ -5419,10 +5419,10 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="C36" t="n">
-        <v>535.999</v>
+        <v>536.568</v>
       </c>
     </row>
     <row r="37">
@@ -5430,10 +5430,10 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="C37" t="n">
-        <v>536.4933</v>
+        <v>537.0384</v>
       </c>
     </row>
     <row r="38">
@@ -5441,10 +5441,10 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="C38" t="n">
-        <v>535.7873</v>
+        <v>536.3165</v>
       </c>
     </row>
     <row r="39">
@@ -5452,10 +5452,10 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="C39" t="n">
-        <v>536.8946</v>
+        <v>537.3692</v>
       </c>
     </row>
     <row r="40">
@@ -5463,10 +5463,10 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="C40" t="n">
-        <v>536.4256</v>
+        <v>536.8377</v>
       </c>
     </row>
     <row r="41">
@@ -5474,10 +5474,10 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="C41" t="n">
-        <v>537.6545</v>
+        <v>538.1932</v>
       </c>
     </row>
     <row r="42">
@@ -5485,10 +5485,10 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="C42" t="n">
-        <v>535.3981</v>
+        <v>535.7643</v>
       </c>
     </row>
     <row r="43">
@@ -5496,10 +5496,10 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="C43" t="n">
-        <v>536.1478</v>
+        <v>536.7227</v>
       </c>
     </row>
     <row r="44">
@@ -5507,10 +5507,10 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="C44" t="n">
-        <v>536.2082</v>
+        <v>536.6768</v>
       </c>
     </row>
     <row r="45">
@@ -5518,10 +5518,10 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="C45" t="n">
-        <v>537.3901</v>
+        <v>537.4057</v>
       </c>
     </row>
     <row r="46">
@@ -5529,10 +5529,10 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="C46" t="n">
-        <v>536.9223</v>
+        <v>537.8469</v>
       </c>
     </row>
     <row r="47">
@@ -5540,10 +5540,10 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="C47" t="n">
-        <v>537.2752</v>
+        <v>537.5747</v>
       </c>
     </row>
     <row r="48">
@@ -5551,10 +5551,10 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="C48" t="n">
-        <v>535.9843</v>
+        <v>536.4648</v>
       </c>
     </row>
     <row r="49">
@@ -5562,10 +5562,10 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="C49" t="n">
-        <v>535.8398</v>
+        <v>536.4167</v>
       </c>
     </row>
     <row r="50">
@@ -5573,10 +5573,10 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="C50" t="n">
-        <v>534.3134</v>
+        <v>534.7362000000001</v>
       </c>
     </row>
     <row r="51">
@@ -5584,10 +5584,10 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="C51" t="n">
-        <v>537.6561</v>
+        <v>538.1711</v>
       </c>
     </row>
     <row r="52">
@@ -5595,10 +5595,10 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="C52" t="n">
-        <v>537.5155</v>
+        <v>538.056</v>
       </c>
     </row>
     <row r="53">
@@ -5606,10 +5606,10 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="C53" t="n">
-        <v>538.2824000000001</v>
+        <v>538.7345</v>
       </c>
     </row>
     <row r="54">
@@ -5617,10 +5617,10 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="C54" t="n">
-        <v>536.7161</v>
+        <v>536.8103</v>
       </c>
     </row>
     <row r="55">
@@ -5628,10 +5628,10 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="C55" t="n">
-        <v>536.4625</v>
+        <v>537.3295000000001</v>
       </c>
     </row>
     <row r="56">
@@ -5639,10 +5639,10 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="C56" t="n">
-        <v>535.8092</v>
+        <v>536.0962</v>
       </c>
     </row>
     <row r="57">
@@ -5650,10 +5650,10 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="C57" t="n">
-        <v>536.8279</v>
+        <v>537.4880000000001</v>
       </c>
     </row>
     <row r="58">
@@ -5661,10 +5661,10 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="C58" t="n">
-        <v>534.7978000000001</v>
+        <v>534.9918</v>
       </c>
     </row>
     <row r="59">
@@ -5672,10 +5672,10 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="C59" t="n">
-        <v>536.0074</v>
+        <v>536.684</v>
       </c>
     </row>
     <row r="60">
@@ -5683,10 +5683,10 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="C60" t="n">
-        <v>536.6351</v>
+        <v>537.0845</v>
       </c>
     </row>
     <row r="61">
@@ -5694,10 +5694,10 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>540.5017</v>
+        <v>540.9817</v>
       </c>
       <c r="C61" t="n">
-        <v>536.6149</v>
+        <v>536.4351</v>
       </c>
     </row>
   </sheetData>

--- a/data/exports/optimization/lotto_genetic_optimizer_results.xlsx
+++ b/data/exports/optimization/lotto_genetic_optimizer_results.xlsx
@@ -565,7 +565,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -685,7 +685,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -865,7 +865,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -925,7 +925,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -985,7 +985,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -1045,7 +1045,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -1465,7 +1465,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -1885,7 +1885,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -2125,7 +2125,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -2305,7 +2305,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -2425,7 +2425,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -2725,7 +2725,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -2845,7 +2845,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -2965,7 +2965,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -3145,7 +3145,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -3325,7 +3325,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -3445,7 +3445,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -3565,7 +3565,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -3625,7 +3625,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -3745,7 +3745,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -3805,7 +3805,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -3925,7 +3925,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -4045,7 +4045,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -4105,7 +4105,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -4165,7 +4165,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -4225,7 +4225,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -4345,7 +4345,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -4405,7 +4405,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -4525,7 +4525,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -4585,7 +4585,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -4645,7 +4645,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -4705,7 +4705,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -4765,7 +4765,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -4885,7 +4885,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>
@@ -5005,7 +5005,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>2026-05-24 05:36:48</t>
+          <t>2026-05-25 14:34:03</t>
         </is>
       </c>
     </row>

--- a/data/exports/optimization/lotto_genetic_optimizer_results.xlsx
+++ b/data/exports/optimization/lotto_genetic_optimizer_results.xlsx
@@ -565,7 +565,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -685,7 +685,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -865,7 +865,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -925,7 +925,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -985,7 +985,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -1045,7 +1045,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -1465,7 +1465,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -1885,7 +1885,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -2125,7 +2125,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -2305,7 +2305,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -2425,7 +2425,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -2725,7 +2725,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -2845,7 +2845,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -2965,7 +2965,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -3145,7 +3145,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -3325,7 +3325,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -3445,7 +3445,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -3565,7 +3565,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -3625,7 +3625,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -3745,7 +3745,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -3805,7 +3805,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -3925,7 +3925,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -4045,7 +4045,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -4105,7 +4105,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -4165,7 +4165,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -4225,7 +4225,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -4345,7 +4345,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -4405,7 +4405,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -4525,7 +4525,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -4585,7 +4585,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -4645,7 +4645,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -4705,7 +4705,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -4765,7 +4765,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -4885,7 +4885,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>
@@ -5005,7 +5005,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:03</t>
+          <t>2026-05-26 14:23:21</t>
         </is>
       </c>
     </row>

--- a/data/exports/optimization/lotto_genetic_optimizer_results.xlsx
+++ b/data/exports/optimization/lotto_genetic_optimizer_results.xlsx
@@ -565,7 +565,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -685,7 +685,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -805,7 +805,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -865,7 +865,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -925,7 +925,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -985,7 +985,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -1045,7 +1045,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -1465,7 +1465,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -1525,7 +1525,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -1885,7 +1885,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -2125,7 +2125,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -2305,7 +2305,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -2425,7 +2425,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -2545,7 +2545,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -2725,7 +2725,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -2785,7 +2785,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -2845,7 +2845,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -2965,7 +2965,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -3145,7 +3145,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -3325,7 +3325,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -3445,7 +3445,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -3565,7 +3565,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -3625,7 +3625,7 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -3745,7 +3745,7 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -3805,7 +3805,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -3865,7 +3865,7 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -3925,7 +3925,7 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -4045,7 +4045,7 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -4105,7 +4105,7 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -4165,7 +4165,7 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -4225,7 +4225,7 @@
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -4345,7 +4345,7 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -4405,7 +4405,7 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -4525,7 +4525,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -4585,7 +4585,7 @@
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -4645,7 +4645,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -4705,7 +4705,7 @@
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -4765,7 +4765,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -4885,7 +4885,7 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>
@@ -5005,7 +5005,7 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:21</t>
+          <t>2026-05-27 14:58:13</t>
         </is>
       </c>
     </row>

--- a/data/exports/optimization/lotto_genetic_optimizer_results.xlsx
+++ b/data/exports/optimization/lotto_genetic_optimizer_results.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R76"/>
+  <dimension ref="A1:W94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -485,25 +485,50 @@
       </c>
       <c r="N1" t="inlineStr">
         <is>
+          <t>Bucket_LOW</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Bucket_MID_LOW</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Bucket_MID_HIGH</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Bucket_HIGH</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Upper50PlusCount</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
           <t>ConsecutivePairs</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>EntropyScore</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>FitnessScore</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>ModelVersion</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>GeneratedAt</t>
         </is>
@@ -514,34 +539,34 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
+        <v>44</v>
+      </c>
+      <c r="E2" t="n">
+        <v>49</v>
+      </c>
+      <c r="F2" t="n">
+        <v>52</v>
+      </c>
+      <c r="G2" t="n">
+        <v>56</v>
+      </c>
+      <c r="H2" t="n">
         <v>8</v>
       </c>
-      <c r="E2" t="n">
-        <v>44</v>
-      </c>
-      <c r="F2" t="n">
-        <v>47</v>
-      </c>
-      <c r="G2" t="n">
-        <v>49</v>
-      </c>
-      <c r="H2" t="n">
-        <v>23</v>
-      </c>
       <c r="I2" t="n">
-        <v>156</v>
+        <v>206</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L2" t="n">
         <v>2</v>
@@ -550,22 +575,37 @@
         <v>4</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O2" t="n">
-        <v>13.3207</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>540.9817</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>3</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>14.519</v>
+      </c>
+      <c r="U2" t="n">
+        <v>312.7093</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -574,34 +614,34 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E3" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F3" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G3" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="H3" t="n">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="I3" t="n">
-        <v>156</v>
+        <v>206</v>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L3" t="n">
         <v>2</v>
@@ -610,22 +650,37 @@
         <v>4</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O3" t="n">
-        <v>13.3207</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>540.9817</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>14.519</v>
+      </c>
+      <c r="U3" t="n">
+        <v>312.7093</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -634,34 +689,34 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E4" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F4" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G4" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I4" t="n">
-        <v>156</v>
+        <v>206</v>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
         <v>2</v>
@@ -670,22 +725,37 @@
         <v>4</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O4" t="n">
-        <v>13.3207</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>540.9817</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>14.519</v>
+      </c>
+      <c r="U4" t="n">
+        <v>312.7093</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -694,34 +764,34 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E5" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F5" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G5" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="H5" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="I5" t="n">
-        <v>156</v>
+        <v>206</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L5" t="n">
         <v>2</v>
@@ -730,22 +800,37 @@
         <v>4</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O5" t="n">
-        <v>13.3207</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>540.9817</v>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>14.519</v>
+      </c>
+      <c r="U5" t="n">
+        <v>312.7093</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -754,34 +839,34 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E6" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F6" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G6" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="H6" t="n">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="I6" t="n">
-        <v>156</v>
+        <v>206</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L6" t="n">
         <v>2</v>
@@ -790,22 +875,37 @@
         <v>4</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O6" t="n">
-        <v>13.3207</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>540.9817</v>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>14.519</v>
+      </c>
+      <c r="U6" t="n">
+        <v>312.7093</v>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -814,34 +914,34 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E7" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F7" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G7" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="H7" t="n">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="I7" t="n">
-        <v>156</v>
+        <v>206</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
         <v>2</v>
@@ -850,22 +950,37 @@
         <v>4</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O7" t="n">
-        <v>13.3207</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>540.9817</v>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>14.519</v>
+      </c>
+      <c r="U7" t="n">
+        <v>312.7093</v>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -874,34 +989,34 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E8" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F8" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G8" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="H8" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="I8" t="n">
-        <v>156</v>
+        <v>206</v>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L8" t="n">
         <v>2</v>
@@ -910,22 +1025,37 @@
         <v>4</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O8" t="n">
-        <v>13.3207</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>540.9817</v>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>14.519</v>
+      </c>
+      <c r="U8" t="n">
+        <v>312.7093</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -934,34 +1064,34 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E9" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F9" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G9" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="H9" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="I9" t="n">
-        <v>156</v>
+        <v>206</v>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
         <v>2</v>
@@ -970,22 +1100,37 @@
         <v>4</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O9" t="n">
-        <v>13.3207</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>540.9817</v>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>14.519</v>
+      </c>
+      <c r="U9" t="n">
+        <v>312.7093</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -994,34 +1139,34 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E10" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F10" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G10" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="H10" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="I10" t="n">
-        <v>156</v>
+        <v>206</v>
       </c>
       <c r="J10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
         <v>2</v>
@@ -1030,22 +1175,37 @@
         <v>4</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O10" t="n">
-        <v>13.3207</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>540.9817</v>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>14.519</v>
+      </c>
+      <c r="U10" t="n">
+        <v>312.7093</v>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -1054,34 +1214,34 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E11" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F11" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G11" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="H11" t="n">
-        <v>58</v>
+        <v>19</v>
       </c>
       <c r="I11" t="n">
-        <v>156</v>
+        <v>206</v>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L11" t="n">
         <v>2</v>
@@ -1090,22 +1250,37 @@
         <v>4</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O11" t="n">
-        <v>13.3207</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>540.9817</v>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>14.519</v>
+      </c>
+      <c r="U11" t="n">
+        <v>312.7093</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -1114,34 +1289,34 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E12" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F12" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G12" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="H12" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="I12" t="n">
-        <v>156</v>
+        <v>206</v>
       </c>
       <c r="J12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L12" t="n">
         <v>2</v>
@@ -1150,22 +1325,37 @@
         <v>4</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O12" t="n">
-        <v>13.3207</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>540.9817</v>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>14.519</v>
+      </c>
+      <c r="U12" t="n">
+        <v>312.7093</v>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -1174,34 +1364,34 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E13" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F13" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G13" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="H13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="I13" t="n">
-        <v>156</v>
+        <v>206</v>
       </c>
       <c r="J13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L13" t="n">
         <v>2</v>
@@ -1210,22 +1400,37 @@
         <v>4</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O13" t="n">
-        <v>13.3207</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>540.9817</v>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>14.519</v>
+      </c>
+      <c r="U13" t="n">
+        <v>312.7093</v>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -1234,34 +1439,34 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E14" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F14" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G14" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="H14" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="I14" t="n">
-        <v>156</v>
+        <v>206</v>
       </c>
       <c r="J14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L14" t="n">
         <v>2</v>
@@ -1270,22 +1475,37 @@
         <v>4</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O14" t="n">
-        <v>13.3207</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>540.9817</v>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>3</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>14.519</v>
+      </c>
+      <c r="U14" t="n">
+        <v>312.7093</v>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -1294,34 +1514,34 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E15" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F15" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G15" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="H15" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="I15" t="n">
-        <v>156</v>
+        <v>206</v>
       </c>
       <c r="J15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L15" t="n">
         <v>2</v>
@@ -1330,22 +1550,37 @@
         <v>4</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O15" t="n">
-        <v>13.3207</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>540.9817</v>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>14.519</v>
+      </c>
+      <c r="U15" t="n">
+        <v>312.7093</v>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -1354,34 +1589,34 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E16" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F16" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G16" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="H16" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="I16" t="n">
-        <v>156</v>
+        <v>206</v>
       </c>
       <c r="J16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L16" t="n">
         <v>2</v>
@@ -1390,22 +1625,37 @@
         <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O16" t="n">
-        <v>13.3207</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>540.9817</v>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>14.519</v>
+      </c>
+      <c r="U16" t="n">
+        <v>312.7093</v>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -1414,34 +1664,34 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E17" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F17" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G17" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="H17" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I17" t="n">
-        <v>156</v>
+        <v>206</v>
       </c>
       <c r="J17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L17" t="n">
         <v>2</v>
@@ -1450,22 +1700,37 @@
         <v>4</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O17" t="n">
-        <v>13.3207</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>540.9817</v>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>14.519</v>
+      </c>
+      <c r="U17" t="n">
+        <v>312.7093</v>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -1474,34 +1739,34 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D18" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E18" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F18" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G18" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="H18" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="I18" t="n">
-        <v>156</v>
+        <v>206</v>
       </c>
       <c r="J18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L18" t="n">
         <v>2</v>
@@ -1510,22 +1775,37 @@
         <v>4</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O18" t="n">
-        <v>13.3207</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>540.9817</v>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>14.519</v>
+      </c>
+      <c r="U18" t="n">
+        <v>312.7093</v>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -1534,34 +1814,34 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E19" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F19" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G19" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="H19" t="n">
-        <v>18</v>
+        <v>58</v>
       </c>
       <c r="I19" t="n">
-        <v>156</v>
+        <v>206</v>
       </c>
       <c r="J19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L19" t="n">
         <v>2</v>
@@ -1570,22 +1850,37 @@
         <v>4</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O19" t="n">
-        <v>13.3207</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>540.9817</v>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>14.519</v>
+      </c>
+      <c r="U19" t="n">
+        <v>312.7093</v>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -1594,34 +1889,34 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E20" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F20" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G20" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="H20" t="n">
-        <v>5</v>
+        <v>54</v>
       </c>
       <c r="I20" t="n">
-        <v>156</v>
+        <v>206</v>
       </c>
       <c r="J20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L20" t="n">
         <v>2</v>
@@ -1630,22 +1925,37 @@
         <v>4</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O20" t="n">
-        <v>13.3207</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>540.9817</v>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3</v>
+      </c>
+      <c r="R20" t="n">
+        <v>2</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>14.519</v>
+      </c>
+      <c r="U20" t="n">
+        <v>312.7093</v>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -1654,34 +1964,34 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E21" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F21" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G21" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="H21" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="I21" t="n">
-        <v>156</v>
+        <v>206</v>
       </c>
       <c r="J21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L21" t="n">
         <v>2</v>
@@ -1690,22 +2000,37 @@
         <v>4</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O21" t="n">
-        <v>13.3207</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>540.9817</v>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3</v>
+      </c>
+      <c r="R21" t="n">
+        <v>2</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>14.519</v>
+      </c>
+      <c r="U21" t="n">
+        <v>312.7093</v>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -1714,34 +2039,34 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D22" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E22" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F22" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G22" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="H22" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="I22" t="n">
-        <v>156</v>
+        <v>206</v>
       </c>
       <c r="J22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L22" t="n">
         <v>2</v>
@@ -1750,22 +2075,37 @@
         <v>4</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O22" t="n">
-        <v>13.3207</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>540.9817</v>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>3</v>
+      </c>
+      <c r="R22" t="n">
+        <v>2</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>14.519</v>
+      </c>
+      <c r="U22" t="n">
+        <v>312.7093</v>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -1774,34 +2114,34 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E23" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F23" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G23" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="H23" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="I23" t="n">
-        <v>156</v>
+        <v>206</v>
       </c>
       <c r="J23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L23" t="n">
         <v>2</v>
@@ -1810,22 +2150,37 @@
         <v>4</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O23" t="n">
-        <v>13.3207</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>540.9817</v>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3</v>
+      </c>
+      <c r="R23" t="n">
+        <v>2</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>14.519</v>
+      </c>
+      <c r="U23" t="n">
+        <v>312.7093</v>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -1834,34 +2189,34 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D24" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E24" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F24" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G24" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="H24" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="I24" t="n">
-        <v>156</v>
+        <v>206</v>
       </c>
       <c r="J24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L24" t="n">
         <v>2</v>
@@ -1870,22 +2225,37 @@
         <v>4</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O24" t="n">
-        <v>13.3207</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>540.9817</v>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>3</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>14.519</v>
+      </c>
+      <c r="U24" t="n">
+        <v>312.7093</v>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -1894,34 +2264,34 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E25" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F25" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G25" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="H25" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="I25" t="n">
-        <v>156</v>
+        <v>206</v>
       </c>
       <c r="J25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L25" t="n">
         <v>2</v>
@@ -1930,22 +2300,37 @@
         <v>4</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O25" t="n">
-        <v>13.3207</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>540.9817</v>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>3</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>14.519</v>
+      </c>
+      <c r="U25" t="n">
+        <v>312.7093</v>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -1954,34 +2339,34 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E26" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F26" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G26" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="H26" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I26" t="n">
-        <v>156</v>
+        <v>206</v>
       </c>
       <c r="J26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L26" t="n">
         <v>2</v>
@@ -1990,22 +2375,37 @@
         <v>4</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O26" t="n">
-        <v>13.3207</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>540.9817</v>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3</v>
+      </c>
+      <c r="R26" t="n">
+        <v>2</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>14.519</v>
+      </c>
+      <c r="U26" t="n">
+        <v>312.7093</v>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -2014,34 +2414,34 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D27" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E27" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F27" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G27" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="H27" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="I27" t="n">
-        <v>156</v>
+        <v>206</v>
       </c>
       <c r="J27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L27" t="n">
         <v>2</v>
@@ -2050,22 +2450,37 @@
         <v>4</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O27" t="n">
-        <v>13.3207</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>540.9817</v>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>3</v>
+      </c>
+      <c r="R27" t="n">
+        <v>2</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>14.519</v>
+      </c>
+      <c r="U27" t="n">
+        <v>312.7093</v>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -2074,34 +2489,34 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C28" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D28" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E28" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F28" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G28" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="H28" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="I28" t="n">
-        <v>156</v>
+        <v>206</v>
       </c>
       <c r="J28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L28" t="n">
         <v>2</v>
@@ -2110,22 +2525,37 @@
         <v>4</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O28" t="n">
-        <v>13.3207</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>540.9817</v>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>3</v>
+      </c>
+      <c r="R28" t="n">
+        <v>2</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>14.519</v>
+      </c>
+      <c r="U28" t="n">
+        <v>312.7093</v>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -2134,34 +2564,34 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E29" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F29" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G29" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="H29" t="n">
-        <v>53</v>
+        <v>9</v>
       </c>
       <c r="I29" t="n">
-        <v>156</v>
+        <v>206</v>
       </c>
       <c r="J29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L29" t="n">
         <v>2</v>
@@ -2170,22 +2600,37 @@
         <v>4</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O29" t="n">
-        <v>13.3207</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>540.9817</v>
-      </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3</v>
+      </c>
+      <c r="R29" t="n">
+        <v>2</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>14.519</v>
+      </c>
+      <c r="U29" t="n">
+        <v>312.7093</v>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -2194,34 +2639,34 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D30" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E30" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F30" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G30" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="H30" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I30" t="n">
-        <v>156</v>
+        <v>206</v>
       </c>
       <c r="J30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L30" t="n">
         <v>2</v>
@@ -2230,22 +2675,37 @@
         <v>4</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O30" t="n">
-        <v>13.3207</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>540.9817</v>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>3</v>
+      </c>
+      <c r="R30" t="n">
+        <v>2</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>14.519</v>
+      </c>
+      <c r="U30" t="n">
+        <v>312.7093</v>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -2254,34 +2714,34 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D31" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E31" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F31" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G31" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="H31" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="I31" t="n">
-        <v>156</v>
+        <v>206</v>
       </c>
       <c r="J31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L31" t="n">
         <v>2</v>
@@ -2290,22 +2750,37 @@
         <v>4</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O31" t="n">
-        <v>13.3207</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>540.9817</v>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3</v>
+      </c>
+      <c r="R31" t="n">
+        <v>2</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>14.519</v>
+      </c>
+      <c r="U31" t="n">
+        <v>312.7093</v>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -2314,34 +2789,34 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D32" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E32" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F32" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G32" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="H32" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="I32" t="n">
-        <v>156</v>
+        <v>206</v>
       </c>
       <c r="J32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L32" t="n">
         <v>2</v>
@@ -2350,22 +2825,37 @@
         <v>4</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O32" t="n">
-        <v>13.3207</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>540.9817</v>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>3</v>
+      </c>
+      <c r="R32" t="n">
+        <v>2</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>14.519</v>
+      </c>
+      <c r="U32" t="n">
+        <v>312.7093</v>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -2377,55 +2867,70 @@
         <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D33" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E33" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F33" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G33" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="H33" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="I33" t="n">
-        <v>155</v>
+        <v>206</v>
       </c>
       <c r="J33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O33" t="n">
-        <v>13.2454</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>538.6134</v>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>3</v>
+      </c>
+      <c r="R33" t="n">
+        <v>2</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>14.519</v>
+      </c>
+      <c r="U33" t="n">
+        <v>312.7093</v>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -2434,58 +2939,73 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C34" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D34" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="E34" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F34" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G34" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="H34" t="n">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="I34" t="n">
-        <v>165</v>
+        <v>206</v>
       </c>
       <c r="J34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O34" t="n">
-        <v>12.2082</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>537.9605</v>
-      </c>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>3</v>
+      </c>
+      <c r="R34" t="n">
+        <v>2</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>14.519</v>
+      </c>
+      <c r="U34" t="n">
+        <v>312.7093</v>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -2494,34 +3014,34 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D35" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E35" t="n">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="F35" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="G35" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="H35" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="I35" t="n">
-        <v>118</v>
+        <v>206</v>
       </c>
       <c r="J35" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K35" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L35" t="n">
         <v>2</v>
@@ -2530,22 +3050,37 @@
         <v>4</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O35" t="n">
-        <v>12.0167</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>537.4216</v>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>3</v>
+      </c>
+      <c r="R35" t="n">
+        <v>2</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>14.519</v>
+      </c>
+      <c r="U35" t="n">
+        <v>312.7093</v>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -2554,34 +3089,34 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D36" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E36" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F36" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G36" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="H36" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="I36" t="n">
-        <v>158</v>
+        <v>206</v>
       </c>
       <c r="J36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L36" t="n">
         <v>2</v>
@@ -2590,22 +3125,37 @@
         <v>4</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O36" t="n">
-        <v>13.5056</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>537.1239</v>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>3</v>
+      </c>
+      <c r="R36" t="n">
+        <v>2</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>14.519</v>
+      </c>
+      <c r="U36" t="n">
+        <v>312.7093</v>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -2614,58 +3164,73 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D37" t="n">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="E37" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F37" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G37" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="H37" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="I37" t="n">
-        <v>161</v>
+        <v>204</v>
       </c>
       <c r="J37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M37" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O37" t="n">
-        <v>11.876</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>536.5501</v>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>3</v>
+      </c>
+      <c r="R37" t="n">
+        <v>2</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>15.5563</v>
+      </c>
+      <c r="U37" t="n">
+        <v>311.4115</v>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -2674,34 +3239,34 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C38" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D38" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E38" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="F38" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="G38" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="H38" t="n">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="I38" t="n">
-        <v>150</v>
+        <v>208</v>
       </c>
       <c r="J38" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L38" t="n">
         <v>2</v>
@@ -2710,22 +3275,37 @@
         <v>4</v>
       </c>
       <c r="N38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O38" t="n">
-        <v>13.0384</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>535.616</v>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>3</v>
+      </c>
+      <c r="R38" t="n">
+        <v>2</v>
+      </c>
+      <c r="S38" t="n">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>14.7594</v>
+      </c>
+      <c r="U38" t="n">
+        <v>309.3026</v>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -2734,34 +3314,34 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C39" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D39" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E39" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F39" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="G39" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="H39" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="I39" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="J39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L39" t="n">
         <v>2</v>
@@ -2770,22 +3350,37 @@
         <v>4</v>
       </c>
       <c r="N39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O39" t="n">
-        <v>13.0384</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>535.616</v>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>3</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>14.6014</v>
+      </c>
+      <c r="U39" t="n">
+        <v>307.9001</v>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -2794,34 +3389,34 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C40" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D40" t="n">
+        <v>39</v>
+      </c>
+      <c r="E40" t="n">
+        <v>44</v>
+      </c>
+      <c r="F40" t="n">
+        <v>52</v>
+      </c>
+      <c r="G40" t="n">
+        <v>56</v>
+      </c>
+      <c r="H40" t="n">
         <v>8</v>
       </c>
-      <c r="E40" t="n">
-        <v>41</v>
-      </c>
-      <c r="F40" t="n">
-        <v>44</v>
-      </c>
-      <c r="G40" t="n">
-        <v>49</v>
-      </c>
-      <c r="H40" t="n">
-        <v>23</v>
-      </c>
       <c r="I40" t="n">
-        <v>150</v>
+        <v>196</v>
       </c>
       <c r="J40" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L40" t="n">
         <v>2</v>
@@ -2830,22 +3425,37 @@
         <v>4</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O40" t="n">
-        <v>11.8423</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>535.4057</v>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>2</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>2</v>
+      </c>
+      <c r="R40" t="n">
+        <v>2</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>12.1161</v>
+      </c>
+      <c r="U40" t="n">
+        <v>306.0651</v>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -2854,58 +3464,73 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C41" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D41" t="n">
+        <v>44</v>
+      </c>
+      <c r="E41" t="n">
+        <v>49</v>
+      </c>
+      <c r="F41" t="n">
+        <v>51</v>
+      </c>
+      <c r="G41" t="n">
+        <v>52</v>
+      </c>
+      <c r="H41" t="n">
         <v>8</v>
       </c>
-      <c r="E41" t="n">
-        <v>14</v>
-      </c>
-      <c r="F41" t="n">
-        <v>47</v>
-      </c>
-      <c r="G41" t="n">
-        <v>49</v>
-      </c>
-      <c r="H41" t="n">
-        <v>23</v>
-      </c>
       <c r="I41" t="n">
-        <v>126</v>
+        <v>201</v>
       </c>
       <c r="J41" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K41" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O41" t="n">
-        <v>11.8929</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>534.0321</v>
-      </c>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>3</v>
+      </c>
+      <c r="R41" t="n">
+        <v>2</v>
+      </c>
+      <c r="S41" t="n">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>14.9586</v>
+      </c>
+      <c r="U41" t="n">
+        <v>305.6291</v>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -2917,55 +3542,70 @@
         <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D42" t="n">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="E42" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F42" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="G42" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="H42" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="I42" t="n">
-        <v>149</v>
+        <v>212</v>
       </c>
       <c r="J42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O42" t="n">
-        <v>14.2352</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>533.1479</v>
-      </c>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>3</v>
+      </c>
+      <c r="R42" t="n">
+        <v>2</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>14.4028</v>
+      </c>
+      <c r="U42" t="n">
+        <v>305.2665</v>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -2974,58 +3614,73 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="D43" t="n">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="E43" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F43" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G43" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="H43" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="I43" t="n">
-        <v>160</v>
+        <v>219</v>
       </c>
       <c r="J43" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M43" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O43" t="n">
-        <v>12.3871</v>
+        <v>1</v>
       </c>
       <c r="P43" t="n">
-        <v>532.6876999999999</v>
-      </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>3</v>
+      </c>
+      <c r="R43" t="n">
+        <v>2</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>9.2736</v>
+      </c>
+      <c r="U43" t="n">
+        <v>304.4511</v>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -3034,28 +3689,28 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="D44" t="n">
         <v>44</v>
       </c>
       <c r="E44" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F44" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G44" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="H44" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="I44" t="n">
-        <v>198</v>
+        <v>230</v>
       </c>
       <c r="J44" t="n">
         <v>4</v>
@@ -3070,22 +3725,37 @@
         <v>4</v>
       </c>
       <c r="N44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O44" t="n">
-        <v>13.4253</v>
+        <v>1</v>
       </c>
       <c r="P44" t="n">
-        <v>532.5634</v>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>3</v>
+      </c>
+      <c r="R44" t="n">
+        <v>2</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>9.2736</v>
+      </c>
+      <c r="U44" t="n">
+        <v>304.3024</v>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -3094,7 +3764,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C45" t="n">
         <v>6</v>
@@ -3103,19 +3773,19 @@
         <v>44</v>
       </c>
       <c r="E45" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F45" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G45" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="H45" t="n">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="I45" t="n">
-        <v>193</v>
+        <v>211</v>
       </c>
       <c r="J45" t="n">
         <v>4</v>
@@ -3124,28 +3794,43 @@
         <v>2</v>
       </c>
       <c r="L45" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M45" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O45" t="n">
-        <v>14.3332</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>532.0929</v>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R45" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>3</v>
+      </c>
+      <c r="R45" t="n">
+        <v>2</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>13.8362</v>
+      </c>
+      <c r="U45" t="n">
+        <v>303.4038</v>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -3154,58 +3839,73 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D46" t="n">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="E46" t="n">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="F46" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="G46" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="H46" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I46" t="n">
-        <v>118</v>
+        <v>195</v>
       </c>
       <c r="J46" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K46" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L46" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O46" t="n">
-        <v>12.8779</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>532.0146999999999</v>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R46" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>2</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>2</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>13.0843</v>
+      </c>
+      <c r="U46" t="n">
+        <v>303.3799</v>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -3214,28 +3914,28 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C47" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D47" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E47" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F47" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="G47" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="H47" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="I47" t="n">
-        <v>187</v>
+        <v>208</v>
       </c>
       <c r="J47" t="n">
         <v>4</v>
@@ -3244,28 +3944,43 @@
         <v>2</v>
       </c>
       <c r="L47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O47" t="n">
-        <v>11.8423</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>531.1657</v>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>3</v>
+      </c>
+      <c r="R47" t="n">
+        <v>2</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>14.5465</v>
+      </c>
+      <c r="U47" t="n">
+        <v>302.9689</v>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -3274,58 +3989,73 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C48" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D48" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="E48" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="F48" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G48" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="H48" t="n">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="I48" t="n">
-        <v>139</v>
+        <v>194</v>
       </c>
       <c r="J48" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K48" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O48" t="n">
-        <v>8.2849</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>530.7123</v>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R48" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>2</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>2</v>
+      </c>
+      <c r="R48" t="n">
+        <v>1</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>12.5698</v>
+      </c>
+      <c r="U48" t="n">
+        <v>302.9242</v>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -3334,58 +4064,73 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C49" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D49" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="E49" t="n">
         <v>44</v>
       </c>
       <c r="F49" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G49" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="H49" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="I49" t="n">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="J49" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O49" t="n">
-        <v>8.867900000000001</v>
+        <v>1</v>
       </c>
       <c r="P49" t="n">
-        <v>529.1898</v>
-      </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R49" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>2</v>
+      </c>
+      <c r="R49" t="n">
+        <v>2</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>8.7407</v>
+      </c>
+      <c r="U49" t="n">
+        <v>302.6302</v>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -3394,28 +4139,28 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C50" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D50" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E50" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F50" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="G50" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="H50" t="n">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="I50" t="n">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="J50" t="n">
         <v>3</v>
@@ -3424,28 +4169,43 @@
         <v>3</v>
       </c>
       <c r="L50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M50" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O50" t="n">
-        <v>12.522</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>529.125</v>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R50" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>2</v>
+      </c>
+      <c r="R50" t="n">
+        <v>1</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>13.0843</v>
+      </c>
+      <c r="U50" t="n">
+        <v>302.5099</v>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -3454,28 +4214,28 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C51" t="n">
+        <v>4</v>
+      </c>
+      <c r="D51" t="n">
         <v>6</v>
       </c>
-      <c r="D51" t="n">
-        <v>8</v>
-      </c>
       <c r="E51" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="F51" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="G51" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="H51" t="n">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="I51" t="n">
-        <v>140</v>
+        <v>163</v>
       </c>
       <c r="J51" t="n">
         <v>3</v>
@@ -3484,28 +4244,43 @@
         <v>3</v>
       </c>
       <c r="L51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O51" t="n">
-        <v>8.6023</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>528.9858</v>
-      </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R51" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>2</v>
+      </c>
+      <c r="R51" t="n">
+        <v>2</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>13.6528</v>
+      </c>
+      <c r="U51" t="n">
+        <v>301.7142</v>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -3514,28 +4289,28 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D52" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E52" t="n">
         <v>44</v>
       </c>
       <c r="F52" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G52" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="H52" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="I52" t="n">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="J52" t="n">
         <v>3</v>
@@ -3544,28 +4319,43 @@
         <v>3</v>
       </c>
       <c r="L52" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M52" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N52" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O52" t="n">
-        <v>13.4373</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>527.3532</v>
-      </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R52" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>2</v>
+      </c>
+      <c r="R52" t="n">
+        <v>1</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>12.0665</v>
+      </c>
+      <c r="U52" t="n">
+        <v>301.6012</v>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -3574,34 +4364,34 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C53" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D53" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="E53" t="n">
         <v>44</v>
       </c>
       <c r="F53" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G53" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="H53" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="I53" t="n">
-        <v>185</v>
+        <v>163</v>
       </c>
       <c r="J53" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L53" t="n">
         <v>3</v>
@@ -3610,22 +4400,37 @@
         <v>3</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O53" t="n">
-        <v>9.134499999999999</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>526.2764</v>
-      </c>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R53" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>2</v>
+      </c>
+      <c r="R53" t="n">
+        <v>1</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>12.0665</v>
+      </c>
+      <c r="U53" t="n">
+        <v>301.6012</v>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -3634,58 +4439,73 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C54" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="D54" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E54" t="n">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="F54" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="G54" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="H54" t="n">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="I54" t="n">
-        <v>136</v>
+        <v>227</v>
       </c>
       <c r="J54" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K54" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M54" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O54" t="n">
-        <v>7.6158</v>
+        <v>1</v>
       </c>
       <c r="P54" t="n">
-        <v>525.6794</v>
-      </c>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R54" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>3</v>
+      </c>
+      <c r="R54" t="n">
+        <v>2</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>8.7407</v>
+      </c>
+      <c r="U54" t="n">
+        <v>300.8202</v>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -3694,34 +4514,34 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C55" t="n">
+        <v>4</v>
+      </c>
+      <c r="D55" t="n">
+        <v>44</v>
+      </c>
+      <c r="E55" t="n">
+        <v>49</v>
+      </c>
+      <c r="F55" t="n">
+        <v>55</v>
+      </c>
+      <c r="G55" t="n">
+        <v>56</v>
+      </c>
+      <c r="H55" t="n">
         <v>8</v>
       </c>
-      <c r="D55" t="n">
-        <v>29</v>
-      </c>
-      <c r="E55" t="n">
-        <v>44</v>
-      </c>
-      <c r="F55" t="n">
-        <v>47</v>
-      </c>
-      <c r="G55" t="n">
-        <v>49</v>
-      </c>
-      <c r="H55" t="n">
-        <v>13</v>
-      </c>
       <c r="I55" t="n">
-        <v>179</v>
+        <v>209</v>
       </c>
       <c r="J55" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L55" t="n">
         <v>3</v>
@@ -3730,22 +4550,37 @@
         <v>3</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O55" t="n">
-        <v>7.3919</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>524.5196999999999</v>
-      </c>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R55" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>3</v>
+      </c>
+      <c r="R55" t="n">
+        <v>2</v>
+      </c>
+      <c r="S55" t="n">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>14.6014</v>
+      </c>
+      <c r="U55" t="n">
+        <v>300.7476</v>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -3754,58 +4589,73 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C56" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D56" t="n">
+        <v>34</v>
+      </c>
+      <c r="E56" t="n">
+        <v>49</v>
+      </c>
+      <c r="F56" t="n">
+        <v>52</v>
+      </c>
+      <c r="G56" t="n">
+        <v>56</v>
+      </c>
+      <c r="H56" t="n">
         <v>8</v>
       </c>
-      <c r="E56" t="n">
-        <v>12</v>
-      </c>
-      <c r="F56" t="n">
-        <v>44</v>
-      </c>
-      <c r="G56" t="n">
-        <v>47</v>
-      </c>
-      <c r="H56" t="n">
-        <v>26</v>
-      </c>
       <c r="I56" t="n">
-        <v>119</v>
+        <v>196</v>
       </c>
       <c r="J56" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K56" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M56" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O56" t="n">
-        <v>11.5239</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>522.1097</v>
-      </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R56" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>3</v>
+      </c>
+      <c r="R56" t="n">
+        <v>2</v>
+      </c>
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>10.5262</v>
+      </c>
+      <c r="U56" t="n">
+        <v>300.4632</v>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -3814,58 +4664,73 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C57" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D57" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E57" t="n">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="F57" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="G57" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="H57" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="I57" t="n">
-        <v>125</v>
+        <v>170</v>
       </c>
       <c r="J57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K57" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M57" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O57" t="n">
-        <v>9.499499999999999</v>
+        <v>1</v>
       </c>
       <c r="P57" t="n">
-        <v>521.2886999999999</v>
-      </c>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R57" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>2</v>
+      </c>
+      <c r="R57" t="n">
+        <v>1</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>9.011100000000001</v>
+      </c>
+      <c r="U57" t="n">
+        <v>300.1598</v>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -3874,28 +4739,28 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" t="n">
+        <v>4</v>
+      </c>
+      <c r="D58" t="n">
+        <v>23</v>
+      </c>
+      <c r="E58" t="n">
+        <v>44</v>
+      </c>
+      <c r="F58" t="n">
+        <v>52</v>
+      </c>
+      <c r="G58" t="n">
+        <v>56</v>
+      </c>
+      <c r="H58" t="n">
         <v>6</v>
       </c>
-      <c r="C58" t="n">
-        <v>8</v>
-      </c>
-      <c r="D58" t="n">
-        <v>25</v>
-      </c>
-      <c r="E58" t="n">
-        <v>44</v>
-      </c>
-      <c r="F58" t="n">
-        <v>47</v>
-      </c>
-      <c r="G58" t="n">
-        <v>49</v>
-      </c>
-      <c r="H58" t="n">
-        <v>37</v>
-      </c>
       <c r="I58" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J58" t="n">
         <v>3</v>
@@ -3904,28 +4769,43 @@
         <v>3</v>
       </c>
       <c r="L58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O58" t="n">
-        <v>7.7097</v>
+        <v>1</v>
       </c>
       <c r="P58" t="n">
-        <v>520.0143</v>
-      </c>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R58" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>2</v>
+      </c>
+      <c r="R58" t="n">
+        <v>2</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>7.5631</v>
+      </c>
+      <c r="U58" t="n">
+        <v>299.3278</v>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -3934,28 +4814,28 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C59" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D59" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E59" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F59" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="G59" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="H59" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="I59" t="n">
-        <v>139</v>
+        <v>171</v>
       </c>
       <c r="J59" t="n">
         <v>3</v>
@@ -3964,28 +4844,43 @@
         <v>3</v>
       </c>
       <c r="L59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M59" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O59" t="n">
-        <v>8.294600000000001</v>
+        <v>1</v>
       </c>
       <c r="P59" t="n">
-        <v>515.1564</v>
-      </c>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R59" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>2</v>
+      </c>
+      <c r="R59" t="n">
+        <v>1</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>8.671799999999999</v>
+      </c>
+      <c r="U59" t="n">
+        <v>298.0785</v>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -3994,28 +4889,28 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C60" t="n">
         <v>4</v>
       </c>
       <c r="D60" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="E60" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F60" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G60" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="H60" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="I60" t="n">
-        <v>152</v>
+        <v>188</v>
       </c>
       <c r="J60" t="n">
         <v>3</v>
@@ -4030,22 +4925,37 @@
         <v>4</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O60" t="n">
-        <v>14.3052</v>
+        <v>1</v>
       </c>
       <c r="P60" t="n">
-        <v>514.9031</v>
-      </c>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R60" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>0</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>3</v>
+      </c>
+      <c r="R60" t="n">
+        <v>2</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>9.402100000000001</v>
+      </c>
+      <c r="U60" t="n">
+        <v>297.8497</v>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -4054,34 +4964,34 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C61" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D61" t="n">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="E61" t="n">
+        <v>49</v>
+      </c>
+      <c r="F61" t="n">
+        <v>52</v>
+      </c>
+      <c r="G61" t="n">
+        <v>56</v>
+      </c>
+      <c r="H61" t="n">
         <v>8</v>
       </c>
-      <c r="F61" t="n">
-        <v>44</v>
-      </c>
-      <c r="G61" t="n">
-        <v>47</v>
-      </c>
-      <c r="H61" t="n">
-        <v>23</v>
-      </c>
       <c r="I61" t="n">
-        <v>112</v>
+        <v>210</v>
       </c>
       <c r="J61" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K61" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L61" t="n">
         <v>2</v>
@@ -4090,22 +5000,37 @@
         <v>4</v>
       </c>
       <c r="N61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O61" t="n">
-        <v>13.5204</v>
+        <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>510.7409</v>
-      </c>
-      <c r="Q61" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R61" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>0</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>4</v>
+      </c>
+      <c r="R61" t="n">
+        <v>2</v>
+      </c>
+      <c r="S61" t="n">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>16.5288</v>
+      </c>
+      <c r="U61" t="n">
+        <v>297.408</v>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -4114,34 +5039,34 @@
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C62" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D62" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="E62" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="F62" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G62" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="H62" t="n">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="I62" t="n">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="J62" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K62" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L62" t="n">
         <v>2</v>
@@ -4150,22 +5075,37 @@
         <v>4</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O62" t="n">
-        <v>10.6132</v>
+        <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>509.533</v>
-      </c>
-      <c r="Q62" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R62" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>0</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>4</v>
+      </c>
+      <c r="R62" t="n">
+        <v>2</v>
+      </c>
+      <c r="S62" t="n">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>16.5288</v>
+      </c>
+      <c r="U62" t="n">
+        <v>297.408</v>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -4174,58 +5114,73 @@
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C63" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D63" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E63" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="F63" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G63" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="H63" t="n">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="I63" t="n">
-        <v>148</v>
+        <v>223</v>
       </c>
       <c r="J63" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K63" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M63" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O63" t="n">
-        <v>9.8712</v>
+        <v>1</v>
       </c>
       <c r="P63" t="n">
-        <v>505.4779</v>
-      </c>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R63" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>3</v>
+      </c>
+      <c r="R63" t="n">
+        <v>2</v>
+      </c>
+      <c r="S63" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>8.7316</v>
+      </c>
+      <c r="U63" t="n">
+        <v>295.5471</v>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -4234,28 +5189,28 @@
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C64" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D64" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E64" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F64" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G64" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="H64" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="I64" t="n">
-        <v>184</v>
+        <v>217</v>
       </c>
       <c r="J64" t="n">
         <v>4</v>
@@ -4264,28 +5219,43 @@
         <v>2</v>
       </c>
       <c r="L64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M64" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O64" t="n">
-        <v>10.4995</v>
+        <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>503.2288</v>
-      </c>
-      <c r="Q64" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R64" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>3</v>
+      </c>
+      <c r="R64" t="n">
+        <v>2</v>
+      </c>
+      <c r="S64" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>10.9289</v>
+      </c>
+      <c r="U64" t="n">
+        <v>295.4446</v>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -4294,58 +5264,73 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C65" t="n">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="D65" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="E65" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F65" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G65" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="H65" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="I65" t="n">
-        <v>181</v>
+        <v>246</v>
       </c>
       <c r="J65" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L65" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M65" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O65" t="n">
-        <v>7.8128</v>
+        <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>502.152</v>
-      </c>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R65" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>2</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>3</v>
+      </c>
+      <c r="R65" t="n">
+        <v>2</v>
+      </c>
+      <c r="S65" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>13.3207</v>
+      </c>
+      <c r="U65" t="n">
+        <v>295.4303</v>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -4354,58 +5339,73 @@
         <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C66" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="D66" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E66" t="n">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="F66" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="G66" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="H66" t="n">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="I66" t="n">
-        <v>132</v>
+        <v>225</v>
       </c>
       <c r="J66" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K66" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M66" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O66" t="n">
-        <v>7.4027</v>
+        <v>1</v>
       </c>
       <c r="P66" t="n">
-        <v>498.5468</v>
-      </c>
-      <c r="Q66" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R66" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>3</v>
+      </c>
+      <c r="R66" t="n">
+        <v>2</v>
+      </c>
+      <c r="S66" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>8.2608</v>
+      </c>
+      <c r="U66" t="n">
+        <v>295.2689</v>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -4414,28 +5414,28 @@
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C67" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D67" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E67" t="n">
         <v>44</v>
       </c>
       <c r="F67" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G67" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="H67" t="n">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="I67" t="n">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="J67" t="n">
         <v>3</v>
@@ -4450,22 +5450,37 @@
         <v>3</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O67" t="n">
-        <v>7.1722</v>
+        <v>1</v>
       </c>
       <c r="P67" t="n">
-        <v>497.7704</v>
-      </c>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R67" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>2</v>
+      </c>
+      <c r="R67" t="n">
+        <v>1</v>
+      </c>
+      <c r="S67" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>9.1739</v>
+      </c>
+      <c r="U67" t="n">
+        <v>294.3144</v>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -4474,28 +5489,28 @@
         <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C68" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D68" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E68" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F68" t="n">
         <v>49</v>
       </c>
       <c r="G68" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="H68" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="I68" t="n">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="J68" t="n">
         <v>3</v>
@@ -4504,28 +5519,43 @@
         <v>3</v>
       </c>
       <c r="L68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M68" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O68" t="n">
-        <v>14.7323</v>
+        <v>1</v>
       </c>
       <c r="P68" t="n">
-        <v>496.5107</v>
-      </c>
-      <c r="Q68" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R68" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>2</v>
+      </c>
+      <c r="R68" t="n">
+        <v>1</v>
+      </c>
+      <c r="S68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>8.099399999999999</v>
+      </c>
+      <c r="U68" t="n">
+        <v>294.2008</v>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -4534,13 +5564,13 @@
         <v>68</v>
       </c>
       <c r="B69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C69" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D69" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="E69" t="n">
         <v>44</v>
@@ -4549,43 +5579,58 @@
         <v>49</v>
       </c>
       <c r="G69" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="H69" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="I69" t="n">
-        <v>160</v>
+        <v>187</v>
       </c>
       <c r="J69" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K69" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M69" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O69" t="n">
-        <v>13.1514</v>
+        <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>492.4786</v>
-      </c>
-      <c r="Q69" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R69" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>2</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>2</v>
+      </c>
+      <c r="R69" t="n">
+        <v>1</v>
+      </c>
+      <c r="S69" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>9.380800000000001</v>
+      </c>
+      <c r="U69" t="n">
+        <v>294.1413</v>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -4594,28 +5639,28 @@
         <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C70" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D70" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="E70" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F70" t="n">
         <v>49</v>
       </c>
       <c r="G70" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="H70" t="n">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="I70" t="n">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="J70" t="n">
         <v>4</v>
@@ -4630,22 +5675,37 @@
         <v>3</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O70" t="n">
-        <v>14.1195</v>
+        <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>490.2187</v>
-      </c>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R70" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>2</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>2</v>
+      </c>
+      <c r="R70" t="n">
+        <v>1</v>
+      </c>
+      <c r="S70" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>9.380800000000001</v>
+      </c>
+      <c r="U70" t="n">
+        <v>294.1413</v>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -4654,28 +5714,28 @@
         <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C71" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="D71" t="n">
         <v>44</v>
       </c>
       <c r="E71" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F71" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G71" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H71" t="n">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="I71" t="n">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="J71" t="n">
         <v>4</v>
@@ -4684,28 +5744,43 @@
         <v>2</v>
       </c>
       <c r="L71" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M71" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O71" t="n">
-        <v>13.1818</v>
+        <v>1</v>
       </c>
       <c r="P71" t="n">
-        <v>458.2145</v>
-      </c>
-      <c r="Q71" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R71" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>3</v>
+      </c>
+      <c r="R71" t="n">
+        <v>2</v>
+      </c>
+      <c r="S71" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>7.9649</v>
+      </c>
+      <c r="U71" t="n">
+        <v>294.0718</v>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -4714,58 +5789,73 @@
         <v>71</v>
       </c>
       <c r="B72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C72" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D72" t="n">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="E72" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F72" t="n">
         <v>49</v>
       </c>
       <c r="G72" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="H72" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I72" t="n">
-        <v>203</v>
+        <v>168</v>
       </c>
       <c r="J72" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L72" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M72" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O72" t="n">
-        <v>12.9677</v>
+        <v>0</v>
       </c>
       <c r="P72" t="n">
-        <v>458.1591</v>
-      </c>
-      <c r="Q72" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R72" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>2</v>
+      </c>
+      <c r="R72" t="n">
+        <v>1</v>
+      </c>
+      <c r="S72" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>9.7775</v>
+      </c>
+      <c r="U72" t="n">
+        <v>293.8396</v>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -4774,28 +5864,28 @@
         <v>72</v>
       </c>
       <c r="B73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C73" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D73" t="n">
+        <v>14</v>
+      </c>
+      <c r="E73" t="n">
+        <v>44</v>
+      </c>
+      <c r="F73" t="n">
+        <v>49</v>
+      </c>
+      <c r="G73" t="n">
+        <v>56</v>
+      </c>
+      <c r="H73" t="n">
         <v>8</v>
       </c>
-      <c r="E73" t="n">
-        <v>44</v>
-      </c>
-      <c r="F73" t="n">
-        <v>49</v>
-      </c>
-      <c r="G73" t="n">
-        <v>55</v>
-      </c>
-      <c r="H73" t="n">
-        <v>23</v>
-      </c>
       <c r="I73" t="n">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="J73" t="n">
         <v>3</v>
@@ -4810,22 +5900,37 @@
         <v>4</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O73" t="n">
-        <v>12.7687</v>
+        <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>457.4818</v>
-      </c>
-      <c r="Q73" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R73" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>2</v>
+      </c>
+      <c r="R73" t="n">
+        <v>1</v>
+      </c>
+      <c r="S73" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>9.7775</v>
+      </c>
+      <c r="U73" t="n">
+        <v>293.8396</v>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -4834,34 +5939,34 @@
         <v>73</v>
       </c>
       <c r="B74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C74" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D74" t="n">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="E74" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F74" t="n">
         <v>49</v>
       </c>
       <c r="G74" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H74" t="n">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="I74" t="n">
-        <v>204</v>
+        <v>162</v>
       </c>
       <c r="J74" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L74" t="n">
         <v>2</v>
@@ -4870,22 +5975,37 @@
         <v>4</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O74" t="n">
-        <v>12.8779</v>
+        <v>0</v>
       </c>
       <c r="P74" t="n">
-        <v>456.7947</v>
-      </c>
-      <c r="Q74" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R74" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>2</v>
+      </c>
+      <c r="R74" t="n">
+        <v>1</v>
+      </c>
+      <c r="S74" t="n">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>11.0526</v>
+      </c>
+      <c r="U74" t="n">
+        <v>293.341</v>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -4894,28 +6014,28 @@
         <v>74</v>
       </c>
       <c r="B75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C75" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D75" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E75" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F75" t="n">
         <v>49</v>
       </c>
       <c r="G75" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="H75" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="I75" t="n">
-        <v>204</v>
+        <v>187</v>
       </c>
       <c r="J75" t="n">
         <v>4</v>
@@ -4924,28 +6044,43 @@
         <v>2</v>
       </c>
       <c r="L75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M75" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O75" t="n">
-        <v>13.7026</v>
+        <v>0</v>
       </c>
       <c r="P75" t="n">
-        <v>456.6764</v>
-      </c>
-      <c r="Q75" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R75" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>2</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>2</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>11.4961</v>
+      </c>
+      <c r="U75" t="n">
+        <v>292.794</v>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -4954,34 +6089,34 @@
         <v>75</v>
       </c>
       <c r="B76" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C76" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D76" t="n">
+        <v>44</v>
+      </c>
+      <c r="E76" t="n">
+        <v>49</v>
+      </c>
+      <c r="F76" t="n">
+        <v>52</v>
+      </c>
+      <c r="G76" t="n">
+        <v>56</v>
+      </c>
+      <c r="H76" t="n">
         <v>8</v>
       </c>
-      <c r="E76" t="n">
-        <v>44</v>
-      </c>
-      <c r="F76" t="n">
-        <v>47</v>
-      </c>
-      <c r="G76" t="n">
-        <v>54</v>
-      </c>
-      <c r="H76" t="n">
-        <v>23</v>
-      </c>
       <c r="I76" t="n">
-        <v>161</v>
+        <v>219</v>
       </c>
       <c r="J76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L76" t="n">
         <v>1</v>
@@ -4990,22 +6125,1387 @@
         <v>5</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O76" t="n">
-        <v>12.9089</v>
+        <v>0</v>
       </c>
       <c r="P76" t="n">
-        <v>446.9123</v>
-      </c>
-      <c r="Q76" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v1</t>
-        </is>
-      </c>
-      <c r="R76" t="inlineStr">
-        <is>
-          <t>2026-05-27 14:58:13</t>
+        <v>1</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>3</v>
+      </c>
+      <c r="R76" t="n">
+        <v>2</v>
+      </c>
+      <c r="S76" t="n">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>10.0916</v>
+      </c>
+      <c r="U76" t="n">
+        <v>292.1677</v>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="n">
+        <v>1</v>
+      </c>
+      <c r="C77" t="n">
+        <v>4</v>
+      </c>
+      <c r="D77" t="n">
+        <v>22</v>
+      </c>
+      <c r="E77" t="n">
+        <v>44</v>
+      </c>
+      <c r="F77" t="n">
+        <v>49</v>
+      </c>
+      <c r="G77" t="n">
+        <v>52</v>
+      </c>
+      <c r="H77" t="n">
+        <v>42</v>
+      </c>
+      <c r="I77" t="n">
+        <v>172</v>
+      </c>
+      <c r="J77" t="n">
+        <v>3</v>
+      </c>
+      <c r="K77" t="n">
+        <v>3</v>
+      </c>
+      <c r="L77" t="n">
+        <v>2</v>
+      </c>
+      <c r="M77" t="n">
+        <v>4</v>
+      </c>
+      <c r="N77" t="n">
+        <v>2</v>
+      </c>
+      <c r="O77" t="n">
+        <v>1</v>
+      </c>
+      <c r="P77" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>2</v>
+      </c>
+      <c r="R77" t="n">
+        <v>1</v>
+      </c>
+      <c r="S77" t="n">
+        <v>0</v>
+      </c>
+      <c r="T77" t="n">
+        <v>8.133900000000001</v>
+      </c>
+      <c r="U77" t="n">
+        <v>291.8924</v>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="n">
+        <v>1</v>
+      </c>
+      <c r="C78" t="n">
+        <v>36</v>
+      </c>
+      <c r="D78" t="n">
+        <v>44</v>
+      </c>
+      <c r="E78" t="n">
+        <v>49</v>
+      </c>
+      <c r="F78" t="n">
+        <v>52</v>
+      </c>
+      <c r="G78" t="n">
+        <v>56</v>
+      </c>
+      <c r="H78" t="n">
+        <v>12</v>
+      </c>
+      <c r="I78" t="n">
+        <v>238</v>
+      </c>
+      <c r="J78" t="n">
+        <v>5</v>
+      </c>
+      <c r="K78" t="n">
+        <v>1</v>
+      </c>
+      <c r="L78" t="n">
+        <v>2</v>
+      </c>
+      <c r="M78" t="n">
+        <v>4</v>
+      </c>
+      <c r="N78" t="n">
+        <v>1</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>3</v>
+      </c>
+      <c r="R78" t="n">
+        <v>2</v>
+      </c>
+      <c r="S78" t="n">
+        <v>0</v>
+      </c>
+      <c r="T78" t="n">
+        <v>12.1161</v>
+      </c>
+      <c r="U78" t="n">
+        <v>291.3988</v>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="n">
+        <v>1</v>
+      </c>
+      <c r="C79" t="n">
+        <v>44</v>
+      </c>
+      <c r="D79" t="n">
+        <v>46</v>
+      </c>
+      <c r="E79" t="n">
+        <v>49</v>
+      </c>
+      <c r="F79" t="n">
+        <v>52</v>
+      </c>
+      <c r="G79" t="n">
+        <v>56</v>
+      </c>
+      <c r="H79" t="n">
+        <v>8</v>
+      </c>
+      <c r="I79" t="n">
+        <v>248</v>
+      </c>
+      <c r="J79" t="n">
+        <v>5</v>
+      </c>
+      <c r="K79" t="n">
+        <v>1</v>
+      </c>
+      <c r="L79" t="n">
+        <v>2</v>
+      </c>
+      <c r="M79" t="n">
+        <v>4</v>
+      </c>
+      <c r="N79" t="n">
+        <v>1</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>4</v>
+      </c>
+      <c r="R79" t="n">
+        <v>2</v>
+      </c>
+      <c r="S79" t="n">
+        <v>0</v>
+      </c>
+      <c r="T79" t="n">
+        <v>16.0125</v>
+      </c>
+      <c r="U79" t="n">
+        <v>291.2412</v>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="n">
+        <v>1</v>
+      </c>
+      <c r="C80" t="n">
+        <v>4</v>
+      </c>
+      <c r="D80" t="n">
+        <v>26</v>
+      </c>
+      <c r="E80" t="n">
+        <v>44</v>
+      </c>
+      <c r="F80" t="n">
+        <v>49</v>
+      </c>
+      <c r="G80" t="n">
+        <v>52</v>
+      </c>
+      <c r="H80" t="n">
+        <v>8</v>
+      </c>
+      <c r="I80" t="n">
+        <v>176</v>
+      </c>
+      <c r="J80" t="n">
+        <v>3</v>
+      </c>
+      <c r="K80" t="n">
+        <v>3</v>
+      </c>
+      <c r="L80" t="n">
+        <v>2</v>
+      </c>
+      <c r="M80" t="n">
+        <v>4</v>
+      </c>
+      <c r="N80" t="n">
+        <v>2</v>
+      </c>
+      <c r="O80" t="n">
+        <v>1</v>
+      </c>
+      <c r="P80" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>2</v>
+      </c>
+      <c r="R80" t="n">
+        <v>1</v>
+      </c>
+      <c r="S80" t="n">
+        <v>0</v>
+      </c>
+      <c r="T80" t="n">
+        <v>8.133900000000001</v>
+      </c>
+      <c r="U80" t="n">
+        <v>290.8461</v>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="n">
+        <v>1</v>
+      </c>
+      <c r="C81" t="n">
+        <v>4</v>
+      </c>
+      <c r="D81" t="n">
+        <v>14</v>
+      </c>
+      <c r="E81" t="n">
+        <v>44</v>
+      </c>
+      <c r="F81" t="n">
+        <v>52</v>
+      </c>
+      <c r="G81" t="n">
+        <v>56</v>
+      </c>
+      <c r="H81" t="n">
+        <v>3</v>
+      </c>
+      <c r="I81" t="n">
+        <v>171</v>
+      </c>
+      <c r="J81" t="n">
+        <v>3</v>
+      </c>
+      <c r="K81" t="n">
+        <v>3</v>
+      </c>
+      <c r="L81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M81" t="n">
+        <v>5</v>
+      </c>
+      <c r="N81" t="n">
+        <v>3</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>2</v>
+      </c>
+      <c r="R81" t="n">
+        <v>2</v>
+      </c>
+      <c r="S81" t="n">
+        <v>0</v>
+      </c>
+      <c r="T81" t="n">
+        <v>9.838699999999999</v>
+      </c>
+      <c r="U81" t="n">
+        <v>290.6771</v>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="n">
+        <v>1</v>
+      </c>
+      <c r="C82" t="n">
+        <v>44</v>
+      </c>
+      <c r="D82" t="n">
+        <v>47</v>
+      </c>
+      <c r="E82" t="n">
+        <v>49</v>
+      </c>
+      <c r="F82" t="n">
+        <v>52</v>
+      </c>
+      <c r="G82" t="n">
+        <v>56</v>
+      </c>
+      <c r="H82" t="n">
+        <v>7</v>
+      </c>
+      <c r="I82" t="n">
+        <v>249</v>
+      </c>
+      <c r="J82" t="n">
+        <v>5</v>
+      </c>
+      <c r="K82" t="n">
+        <v>1</v>
+      </c>
+      <c r="L82" t="n">
+        <v>3</v>
+      </c>
+      <c r="M82" t="n">
+        <v>3</v>
+      </c>
+      <c r="N82" t="n">
+        <v>1</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>4</v>
+      </c>
+      <c r="R82" t="n">
+        <v>2</v>
+      </c>
+      <c r="S82" t="n">
+        <v>0</v>
+      </c>
+      <c r="T82" t="n">
+        <v>16.0125</v>
+      </c>
+      <c r="U82" t="n">
+        <v>290.5037</v>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="n">
+        <v>1</v>
+      </c>
+      <c r="C83" t="n">
+        <v>4</v>
+      </c>
+      <c r="D83" t="n">
+        <v>34</v>
+      </c>
+      <c r="E83" t="n">
+        <v>44</v>
+      </c>
+      <c r="F83" t="n">
+        <v>52</v>
+      </c>
+      <c r="G83" t="n">
+        <v>56</v>
+      </c>
+      <c r="H83" t="n">
+        <v>42</v>
+      </c>
+      <c r="I83" t="n">
+        <v>191</v>
+      </c>
+      <c r="J83" t="n">
+        <v>4</v>
+      </c>
+      <c r="K83" t="n">
+        <v>2</v>
+      </c>
+      <c r="L83" t="n">
+        <v>1</v>
+      </c>
+      <c r="M83" t="n">
+        <v>5</v>
+      </c>
+      <c r="N83" t="n">
+        <v>2</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>2</v>
+      </c>
+      <c r="R83" t="n">
+        <v>2</v>
+      </c>
+      <c r="S83" t="n">
+        <v>0</v>
+      </c>
+      <c r="T83" t="n">
+        <v>9.838699999999999</v>
+      </c>
+      <c r="U83" t="n">
+        <v>289.9596</v>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="n">
+        <v>1</v>
+      </c>
+      <c r="C84" t="n">
+        <v>4</v>
+      </c>
+      <c r="D84" t="n">
+        <v>32</v>
+      </c>
+      <c r="E84" t="n">
+        <v>44</v>
+      </c>
+      <c r="F84" t="n">
+        <v>49</v>
+      </c>
+      <c r="G84" t="n">
+        <v>52</v>
+      </c>
+      <c r="H84" t="n">
+        <v>8</v>
+      </c>
+      <c r="I84" t="n">
+        <v>182</v>
+      </c>
+      <c r="J84" t="n">
+        <v>4</v>
+      </c>
+      <c r="K84" t="n">
+        <v>2</v>
+      </c>
+      <c r="L84" t="n">
+        <v>2</v>
+      </c>
+      <c r="M84" t="n">
+        <v>4</v>
+      </c>
+      <c r="N84" t="n">
+        <v>2</v>
+      </c>
+      <c r="O84" t="n">
+        <v>0</v>
+      </c>
+      <c r="P84" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>2</v>
+      </c>
+      <c r="R84" t="n">
+        <v>1</v>
+      </c>
+      <c r="S84" t="n">
+        <v>0</v>
+      </c>
+      <c r="T84" t="n">
+        <v>9.4953</v>
+      </c>
+      <c r="U84" t="n">
+        <v>289.8392</v>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="n">
+        <v>1</v>
+      </c>
+      <c r="C85" t="n">
+        <v>4</v>
+      </c>
+      <c r="D85" t="n">
+        <v>44</v>
+      </c>
+      <c r="E85" t="n">
+        <v>52</v>
+      </c>
+      <c r="F85" t="n">
+        <v>56</v>
+      </c>
+      <c r="G85" t="n">
+        <v>57</v>
+      </c>
+      <c r="H85" t="n">
+        <v>57</v>
+      </c>
+      <c r="I85" t="n">
+        <v>214</v>
+      </c>
+      <c r="J85" t="n">
+        <v>4</v>
+      </c>
+      <c r="K85" t="n">
+        <v>2</v>
+      </c>
+      <c r="L85" t="n">
+        <v>2</v>
+      </c>
+      <c r="M85" t="n">
+        <v>4</v>
+      </c>
+      <c r="N85" t="n">
+        <v>2</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0</v>
+      </c>
+      <c r="P85" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>3</v>
+      </c>
+      <c r="R85" t="n">
+        <v>3</v>
+      </c>
+      <c r="S85" t="n">
+        <v>1</v>
+      </c>
+      <c r="T85" t="n">
+        <v>14.5794</v>
+      </c>
+      <c r="U85" t="n">
+        <v>289.8049</v>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="n">
+        <v>4</v>
+      </c>
+      <c r="C86" t="n">
+        <v>37</v>
+      </c>
+      <c r="D86" t="n">
+        <v>44</v>
+      </c>
+      <c r="E86" t="n">
+        <v>49</v>
+      </c>
+      <c r="F86" t="n">
+        <v>52</v>
+      </c>
+      <c r="G86" t="n">
+        <v>56</v>
+      </c>
+      <c r="H86" t="n">
+        <v>18</v>
+      </c>
+      <c r="I86" t="n">
+        <v>242</v>
+      </c>
+      <c r="J86" t="n">
+        <v>5</v>
+      </c>
+      <c r="K86" t="n">
+        <v>1</v>
+      </c>
+      <c r="L86" t="n">
+        <v>2</v>
+      </c>
+      <c r="M86" t="n">
+        <v>4</v>
+      </c>
+      <c r="N86" t="n">
+        <v>1</v>
+      </c>
+      <c r="O86" t="n">
+        <v>0</v>
+      </c>
+      <c r="P86" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>3</v>
+      </c>
+      <c r="R86" t="n">
+        <v>2</v>
+      </c>
+      <c r="S86" t="n">
+        <v>0</v>
+      </c>
+      <c r="T86" t="n">
+        <v>11.3772</v>
+      </c>
+      <c r="U86" t="n">
+        <v>289.1023</v>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="n">
+        <v>1</v>
+      </c>
+      <c r="C87" t="n">
+        <v>4</v>
+      </c>
+      <c r="D87" t="n">
+        <v>44</v>
+      </c>
+      <c r="E87" t="n">
+        <v>52</v>
+      </c>
+      <c r="F87" t="n">
+        <v>55</v>
+      </c>
+      <c r="G87" t="n">
+        <v>56</v>
+      </c>
+      <c r="H87" t="n">
+        <v>20</v>
+      </c>
+      <c r="I87" t="n">
+        <v>212</v>
+      </c>
+      <c r="J87" t="n">
+        <v>4</v>
+      </c>
+      <c r="K87" t="n">
+        <v>2</v>
+      </c>
+      <c r="L87" t="n">
+        <v>2</v>
+      </c>
+      <c r="M87" t="n">
+        <v>4</v>
+      </c>
+      <c r="N87" t="n">
+        <v>2</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>3</v>
+      </c>
+      <c r="R87" t="n">
+        <v>3</v>
+      </c>
+      <c r="S87" t="n">
+        <v>1</v>
+      </c>
+      <c r="T87" t="n">
+        <v>14.6833</v>
+      </c>
+      <c r="U87" t="n">
+        <v>288.9958</v>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="n">
+        <v>1</v>
+      </c>
+      <c r="C88" t="n">
+        <v>34</v>
+      </c>
+      <c r="D88" t="n">
+        <v>44</v>
+      </c>
+      <c r="E88" t="n">
+        <v>49</v>
+      </c>
+      <c r="F88" t="n">
+        <v>52</v>
+      </c>
+      <c r="G88" t="n">
+        <v>56</v>
+      </c>
+      <c r="H88" t="n">
+        <v>8</v>
+      </c>
+      <c r="I88" t="n">
+        <v>236</v>
+      </c>
+      <c r="J88" t="n">
+        <v>5</v>
+      </c>
+      <c r="K88" t="n">
+        <v>1</v>
+      </c>
+      <c r="L88" t="n">
+        <v>2</v>
+      </c>
+      <c r="M88" t="n">
+        <v>4</v>
+      </c>
+      <c r="N88" t="n">
+        <v>1</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>3</v>
+      </c>
+      <c r="R88" t="n">
+        <v>2</v>
+      </c>
+      <c r="S88" t="n">
+        <v>0</v>
+      </c>
+      <c r="T88" t="n">
+        <v>11.2606</v>
+      </c>
+      <c r="U88" t="n">
+        <v>287.887</v>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="n">
+        <v>1</v>
+      </c>
+      <c r="C89" t="n">
+        <v>4</v>
+      </c>
+      <c r="D89" t="n">
+        <v>49</v>
+      </c>
+      <c r="E89" t="n">
+        <v>51</v>
+      </c>
+      <c r="F89" t="n">
+        <v>52</v>
+      </c>
+      <c r="G89" t="n">
+        <v>56</v>
+      </c>
+      <c r="H89" t="n">
+        <v>8</v>
+      </c>
+      <c r="I89" t="n">
+        <v>213</v>
+      </c>
+      <c r="J89" t="n">
+        <v>4</v>
+      </c>
+      <c r="K89" t="n">
+        <v>2</v>
+      </c>
+      <c r="L89" t="n">
+        <v>3</v>
+      </c>
+      <c r="M89" t="n">
+        <v>3</v>
+      </c>
+      <c r="N89" t="n">
+        <v>2</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>4</v>
+      </c>
+      <c r="R89" t="n">
+        <v>3</v>
+      </c>
+      <c r="S89" t="n">
+        <v>1</v>
+      </c>
+      <c r="T89" t="n">
+        <v>17.0294</v>
+      </c>
+      <c r="U89" t="n">
+        <v>287.2235</v>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="n">
+        <v>1</v>
+      </c>
+      <c r="C90" t="n">
+        <v>4</v>
+      </c>
+      <c r="D90" t="n">
+        <v>30</v>
+      </c>
+      <c r="E90" t="n">
+        <v>44</v>
+      </c>
+      <c r="F90" t="n">
+        <v>49</v>
+      </c>
+      <c r="G90" t="n">
+        <v>52</v>
+      </c>
+      <c r="H90" t="n">
+        <v>7</v>
+      </c>
+      <c r="I90" t="n">
+        <v>180</v>
+      </c>
+      <c r="J90" t="n">
+        <v>4</v>
+      </c>
+      <c r="K90" t="n">
+        <v>2</v>
+      </c>
+      <c r="L90" t="n">
+        <v>2</v>
+      </c>
+      <c r="M90" t="n">
+        <v>4</v>
+      </c>
+      <c r="N90" t="n">
+        <v>2</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>2</v>
+      </c>
+      <c r="R90" t="n">
+        <v>1</v>
+      </c>
+      <c r="S90" t="n">
+        <v>0</v>
+      </c>
+      <c r="T90" t="n">
+        <v>8.885899999999999</v>
+      </c>
+      <c r="U90" t="n">
+        <v>286.7231</v>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="n">
+        <v>4</v>
+      </c>
+      <c r="C91" t="n">
+        <v>35</v>
+      </c>
+      <c r="D91" t="n">
+        <v>44</v>
+      </c>
+      <c r="E91" t="n">
+        <v>49</v>
+      </c>
+      <c r="F91" t="n">
+        <v>52</v>
+      </c>
+      <c r="G91" t="n">
+        <v>56</v>
+      </c>
+      <c r="H91" t="n">
+        <v>8</v>
+      </c>
+      <c r="I91" t="n">
+        <v>240</v>
+      </c>
+      <c r="J91" t="n">
+        <v>5</v>
+      </c>
+      <c r="K91" t="n">
+        <v>1</v>
+      </c>
+      <c r="L91" t="n">
+        <v>2</v>
+      </c>
+      <c r="M91" t="n">
+        <v>4</v>
+      </c>
+      <c r="N91" t="n">
+        <v>1</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>3</v>
+      </c>
+      <c r="R91" t="n">
+        <v>2</v>
+      </c>
+      <c r="S91" t="n">
+        <v>0</v>
+      </c>
+      <c r="T91" t="n">
+        <v>10.4995</v>
+      </c>
+      <c r="U91" t="n">
+        <v>286.3649</v>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="n">
+        <v>1</v>
+      </c>
+      <c r="C92" t="n">
+        <v>31</v>
+      </c>
+      <c r="D92" t="n">
+        <v>44</v>
+      </c>
+      <c r="E92" t="n">
+        <v>49</v>
+      </c>
+      <c r="F92" t="n">
+        <v>52</v>
+      </c>
+      <c r="G92" t="n">
+        <v>56</v>
+      </c>
+      <c r="H92" t="n">
+        <v>7</v>
+      </c>
+      <c r="I92" t="n">
+        <v>233</v>
+      </c>
+      <c r="J92" t="n">
+        <v>5</v>
+      </c>
+      <c r="K92" t="n">
+        <v>1</v>
+      </c>
+      <c r="L92" t="n">
+        <v>3</v>
+      </c>
+      <c r="M92" t="n">
+        <v>3</v>
+      </c>
+      <c r="N92" t="n">
+        <v>1</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0</v>
+      </c>
+      <c r="P92" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>3</v>
+      </c>
+      <c r="R92" t="n">
+        <v>2</v>
+      </c>
+      <c r="S92" t="n">
+        <v>0</v>
+      </c>
+      <c r="T92" t="n">
+        <v>10.139</v>
+      </c>
+      <c r="U92" t="n">
+        <v>285.2093</v>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="n">
+        <v>1</v>
+      </c>
+      <c r="C93" t="n">
+        <v>31</v>
+      </c>
+      <c r="D93" t="n">
+        <v>44</v>
+      </c>
+      <c r="E93" t="n">
+        <v>49</v>
+      </c>
+      <c r="F93" t="n">
+        <v>52</v>
+      </c>
+      <c r="G93" t="n">
+        <v>56</v>
+      </c>
+      <c r="H93" t="n">
+        <v>57</v>
+      </c>
+      <c r="I93" t="n">
+        <v>233</v>
+      </c>
+      <c r="J93" t="n">
+        <v>5</v>
+      </c>
+      <c r="K93" t="n">
+        <v>1</v>
+      </c>
+      <c r="L93" t="n">
+        <v>3</v>
+      </c>
+      <c r="M93" t="n">
+        <v>3</v>
+      </c>
+      <c r="N93" t="n">
+        <v>1</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0</v>
+      </c>
+      <c r="P93" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>3</v>
+      </c>
+      <c r="R93" t="n">
+        <v>2</v>
+      </c>
+      <c r="S93" t="n">
+        <v>0</v>
+      </c>
+      <c r="T93" t="n">
+        <v>10.139</v>
+      </c>
+      <c r="U93" t="n">
+        <v>285.2093</v>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="n">
+        <v>1</v>
+      </c>
+      <c r="C94" t="n">
+        <v>4</v>
+      </c>
+      <c r="D94" t="n">
+        <v>49</v>
+      </c>
+      <c r="E94" t="n">
+        <v>52</v>
+      </c>
+      <c r="F94" t="n">
+        <v>56</v>
+      </c>
+      <c r="G94" t="n">
+        <v>58</v>
+      </c>
+      <c r="H94" t="n">
+        <v>3</v>
+      </c>
+      <c r="I94" t="n">
+        <v>220</v>
+      </c>
+      <c r="J94" t="n">
+        <v>4</v>
+      </c>
+      <c r="K94" t="n">
+        <v>2</v>
+      </c>
+      <c r="L94" t="n">
+        <v>2</v>
+      </c>
+      <c r="M94" t="n">
+        <v>4</v>
+      </c>
+      <c r="N94" t="n">
+        <v>2</v>
+      </c>
+      <c r="O94" t="n">
+        <v>0</v>
+      </c>
+      <c r="P94" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>4</v>
+      </c>
+      <c r="R94" t="n">
+        <v>3</v>
+      </c>
+      <c r="S94" t="n">
+        <v>0</v>
+      </c>
+      <c r="T94" t="n">
+        <v>16.8119</v>
+      </c>
+      <c r="U94" t="n">
+        <v>282.5296</v>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>LottoGeneticOptimizer_v2_range_balanced</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>2026-05-28 08:54:19</t>
         </is>
       </c>
     </row>
@@ -5020,7 +7520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C61"/>
+  <dimension ref="A1:C71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5045,10 +7545,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>518.9601</v>
+        <v>298.1834</v>
       </c>
       <c r="C2" t="n">
-        <v>439.0952</v>
+        <v>256.2051</v>
       </c>
     </row>
     <row r="3">
@@ -5056,10 +7556,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>524.3188</v>
+        <v>302.4646</v>
       </c>
       <c r="C3" t="n">
-        <v>500.2401</v>
+        <v>276.7191</v>
       </c>
     </row>
     <row r="4">
@@ -5067,10 +7567,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>529.0447</v>
+        <v>306.3161</v>
       </c>
       <c r="C4" t="n">
-        <v>506.6022</v>
+        <v>280.3123</v>
       </c>
     </row>
     <row r="5">
@@ -5078,10 +7578,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>540.3200000000001</v>
+        <v>309.2925</v>
       </c>
       <c r="C5" t="n">
-        <v>512.8799</v>
+        <v>286.1664</v>
       </c>
     </row>
     <row r="6">
@@ -5089,10 +7589,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>540.3200000000001</v>
+        <v>310.3221</v>
       </c>
       <c r="C6" t="n">
-        <v>518.1374</v>
+        <v>288.7889</v>
       </c>
     </row>
     <row r="7">
@@ -5100,10 +7600,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>540.3200000000001</v>
+        <v>310.7661</v>
       </c>
       <c r="C7" t="n">
-        <v>521.7063000000001</v>
+        <v>289.557</v>
       </c>
     </row>
     <row r="8">
@@ -5111,10 +7611,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>540.9817</v>
+        <v>310.7661</v>
       </c>
       <c r="C8" t="n">
-        <v>525.8828999999999</v>
+        <v>289.8532</v>
       </c>
     </row>
     <row r="9">
@@ -5122,10 +7622,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>540.9817</v>
+        <v>310.7661</v>
       </c>
       <c r="C9" t="n">
-        <v>529.317</v>
+        <v>293.8831</v>
       </c>
     </row>
     <row r="10">
@@ -5133,10 +7633,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>540.9817</v>
+        <v>310.7661</v>
       </c>
       <c r="C10" t="n">
-        <v>531.9712</v>
+        <v>295.7263</v>
       </c>
     </row>
     <row r="11">
@@ -5144,10 +7644,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>540.9817</v>
+        <v>312.3839</v>
       </c>
       <c r="C11" t="n">
-        <v>536.4147</v>
+        <v>297.3298</v>
       </c>
     </row>
     <row r="12">
@@ -5155,10 +7655,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>540.9817</v>
+        <v>312.7093</v>
       </c>
       <c r="C12" t="n">
-        <v>536.096</v>
+        <v>302.5974</v>
       </c>
     </row>
     <row r="13">
@@ -5166,10 +7666,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>540.9817</v>
+        <v>312.7093</v>
       </c>
       <c r="C13" t="n">
-        <v>535.7974</v>
+        <v>304.6619</v>
       </c>
     </row>
     <row r="14">
@@ -5177,10 +7677,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>540.9817</v>
+        <v>312.7093</v>
       </c>
       <c r="C14" t="n">
-        <v>536.5204</v>
+        <v>301.8013</v>
       </c>
     </row>
     <row r="15">
@@ -5188,10 +7688,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>540.9817</v>
+        <v>312.7093</v>
       </c>
       <c r="C15" t="n">
-        <v>538.2291</v>
+        <v>298.98</v>
       </c>
     </row>
     <row r="16">
@@ -5199,10 +7699,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>540.9817</v>
+        <v>312.7093</v>
       </c>
       <c r="C16" t="n">
-        <v>538.3438</v>
+        <v>302.7916</v>
       </c>
     </row>
     <row r="17">
@@ -5210,10 +7710,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>540.9817</v>
+        <v>312.7093</v>
       </c>
       <c r="C17" t="n">
-        <v>535.6775</v>
+        <v>308.5304</v>
       </c>
     </row>
     <row r="18">
@@ -5221,10 +7721,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>540.9817</v>
+        <v>312.7093</v>
       </c>
       <c r="C18" t="n">
-        <v>538.1394</v>
+        <v>309.2483</v>
       </c>
     </row>
     <row r="19">
@@ -5232,10 +7732,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>540.9817</v>
+        <v>312.7093</v>
       </c>
       <c r="C19" t="n">
-        <v>537.475</v>
+        <v>310.2212</v>
       </c>
     </row>
     <row r="20">
@@ -5243,10 +7743,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>540.9817</v>
+        <v>312.7093</v>
       </c>
       <c r="C20" t="n">
-        <v>535.9163</v>
+        <v>309.1595</v>
       </c>
     </row>
     <row r="21">
@@ -5254,10 +7754,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>540.9817</v>
+        <v>312.7093</v>
       </c>
       <c r="C21" t="n">
-        <v>536.3330999999999</v>
+        <v>310.043</v>
       </c>
     </row>
     <row r="22">
@@ -5265,10 +7765,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>540.9817</v>
+        <v>312.7093</v>
       </c>
       <c r="C22" t="n">
-        <v>537.3239</v>
+        <v>309.8011</v>
       </c>
     </row>
     <row r="23">
@@ -5276,10 +7776,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>540.9817</v>
+        <v>312.7093</v>
       </c>
       <c r="C23" t="n">
-        <v>536.9828</v>
+        <v>309.6977</v>
       </c>
     </row>
     <row r="24">
@@ -5287,10 +7787,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>540.9817</v>
+        <v>312.7093</v>
       </c>
       <c r="C24" t="n">
-        <v>537.4806</v>
+        <v>309.4656</v>
       </c>
     </row>
     <row r="25">
@@ -5298,10 +7798,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>540.9817</v>
+        <v>312.7093</v>
       </c>
       <c r="C25" t="n">
-        <v>537.7269</v>
+        <v>309.942</v>
       </c>
     </row>
     <row r="26">
@@ -5309,10 +7809,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>540.9817</v>
+        <v>312.7093</v>
       </c>
       <c r="C26" t="n">
-        <v>537.9197</v>
+        <v>309.6856</v>
       </c>
     </row>
     <row r="27">
@@ -5320,10 +7820,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>540.9817</v>
+        <v>312.7093</v>
       </c>
       <c r="C27" t="n">
-        <v>536.4245</v>
+        <v>309.3516</v>
       </c>
     </row>
     <row r="28">
@@ -5331,10 +7831,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>540.9817</v>
+        <v>312.7093</v>
       </c>
       <c r="C28" t="n">
-        <v>536.6409</v>
+        <v>309.154</v>
       </c>
     </row>
     <row r="29">
@@ -5342,10 +7842,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>540.9817</v>
+        <v>312.7093</v>
       </c>
       <c r="C29" t="n">
-        <v>536.2771</v>
+        <v>310.0958</v>
       </c>
     </row>
     <row r="30">
@@ -5353,10 +7853,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>540.9817</v>
+        <v>312.7093</v>
       </c>
       <c r="C30" t="n">
-        <v>537.9097</v>
+        <v>309.2065</v>
       </c>
     </row>
     <row r="31">
@@ -5364,10 +7864,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>540.9817</v>
+        <v>312.7093</v>
       </c>
       <c r="C31" t="n">
-        <v>537.1289</v>
+        <v>309.1689</v>
       </c>
     </row>
     <row r="32">
@@ -5375,10 +7875,10 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>540.9817</v>
+        <v>312.7093</v>
       </c>
       <c r="C32" t="n">
-        <v>537.7095</v>
+        <v>309.7652</v>
       </c>
     </row>
     <row r="33">
@@ -5386,10 +7886,10 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>540.9817</v>
+        <v>312.7093</v>
       </c>
       <c r="C33" t="n">
-        <v>535.6396</v>
+        <v>309.6731</v>
       </c>
     </row>
     <row r="34">
@@ -5397,10 +7897,10 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>540.9817</v>
+        <v>312.7093</v>
       </c>
       <c r="C34" t="n">
-        <v>536.7017</v>
+        <v>309.866</v>
       </c>
     </row>
     <row r="35">
@@ -5408,10 +7908,10 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>540.9817</v>
+        <v>312.7093</v>
       </c>
       <c r="C35" t="n">
-        <v>536.4136999999999</v>
+        <v>309.7693</v>
       </c>
     </row>
     <row r="36">
@@ -5419,10 +7919,10 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>540.9817</v>
+        <v>312.7093</v>
       </c>
       <c r="C36" t="n">
-        <v>536.568</v>
+        <v>309.9437</v>
       </c>
     </row>
     <row r="37">
@@ -5430,10 +7930,10 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>540.9817</v>
+        <v>312.7093</v>
       </c>
       <c r="C37" t="n">
-        <v>537.0384</v>
+        <v>309.6133</v>
       </c>
     </row>
     <row r="38">
@@ -5441,10 +7941,10 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>540.9817</v>
+        <v>312.7093</v>
       </c>
       <c r="C38" t="n">
-        <v>536.3165</v>
+        <v>309.2757</v>
       </c>
     </row>
     <row r="39">
@@ -5452,10 +7952,10 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>540.9817</v>
+        <v>312.7093</v>
       </c>
       <c r="C39" t="n">
-        <v>537.3692</v>
+        <v>309.6936</v>
       </c>
     </row>
     <row r="40">
@@ -5463,10 +7963,10 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>540.9817</v>
+        <v>312.7093</v>
       </c>
       <c r="C40" t="n">
-        <v>536.8377</v>
+        <v>309.7769</v>
       </c>
     </row>
     <row r="41">
@@ -5474,10 +7974,10 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>540.9817</v>
+        <v>312.7093</v>
       </c>
       <c r="C41" t="n">
-        <v>538.1932</v>
+        <v>309.5322</v>
       </c>
     </row>
     <row r="42">
@@ -5485,10 +7985,10 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>540.9817</v>
+        <v>312.7093</v>
       </c>
       <c r="C42" t="n">
-        <v>535.7643</v>
+        <v>309.2596</v>
       </c>
     </row>
     <row r="43">
@@ -5496,10 +7996,10 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>540.9817</v>
+        <v>312.7093</v>
       </c>
       <c r="C43" t="n">
-        <v>536.7227</v>
+        <v>310.3059</v>
       </c>
     </row>
     <row r="44">
@@ -5507,10 +8007,10 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>540.9817</v>
+        <v>312.7093</v>
       </c>
       <c r="C44" t="n">
-        <v>536.6768</v>
+        <v>309.8117</v>
       </c>
     </row>
     <row r="45">
@@ -5518,10 +8018,10 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>540.9817</v>
+        <v>312.7093</v>
       </c>
       <c r="C45" t="n">
-        <v>537.4057</v>
+        <v>309.3354</v>
       </c>
     </row>
     <row r="46">
@@ -5529,10 +8029,10 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>540.9817</v>
+        <v>312.7093</v>
       </c>
       <c r="C46" t="n">
-        <v>537.8469</v>
+        <v>309.4965</v>
       </c>
     </row>
     <row r="47">
@@ -5540,10 +8040,10 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>540.9817</v>
+        <v>312.7093</v>
       </c>
       <c r="C47" t="n">
-        <v>537.5747</v>
+        <v>309.7624</v>
       </c>
     </row>
     <row r="48">
@@ -5551,10 +8051,10 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>540.9817</v>
+        <v>312.7093</v>
       </c>
       <c r="C48" t="n">
-        <v>536.4648</v>
+        <v>308.8788</v>
       </c>
     </row>
     <row r="49">
@@ -5562,10 +8062,10 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>540.9817</v>
+        <v>312.7093</v>
       </c>
       <c r="C49" t="n">
-        <v>536.4167</v>
+        <v>309.4504</v>
       </c>
     </row>
     <row r="50">
@@ -5573,10 +8073,10 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>540.9817</v>
+        <v>312.7093</v>
       </c>
       <c r="C50" t="n">
-        <v>534.7362000000001</v>
+        <v>309.6912</v>
       </c>
     </row>
     <row r="51">
@@ -5584,10 +8084,10 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>540.9817</v>
+        <v>312.7093</v>
       </c>
       <c r="C51" t="n">
-        <v>538.1711</v>
+        <v>309.6809</v>
       </c>
     </row>
     <row r="52">
@@ -5595,10 +8095,10 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>540.9817</v>
+        <v>312.7093</v>
       </c>
       <c r="C52" t="n">
-        <v>538.056</v>
+        <v>309.8251</v>
       </c>
     </row>
     <row r="53">
@@ -5606,10 +8106,10 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>540.9817</v>
+        <v>312.7093</v>
       </c>
       <c r="C53" t="n">
-        <v>538.7345</v>
+        <v>309.7498</v>
       </c>
     </row>
     <row r="54">
@@ -5617,10 +8117,10 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>540.9817</v>
+        <v>312.7093</v>
       </c>
       <c r="C54" t="n">
-        <v>536.8103</v>
+        <v>310.1662</v>
       </c>
     </row>
     <row r="55">
@@ -5628,10 +8128,10 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>540.9817</v>
+        <v>312.7093</v>
       </c>
       <c r="C55" t="n">
-        <v>537.3295000000001</v>
+        <v>309.3211</v>
       </c>
     </row>
     <row r="56">
@@ -5639,10 +8139,10 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>540.9817</v>
+        <v>312.7093</v>
       </c>
       <c r="C56" t="n">
-        <v>536.0962</v>
+        <v>308.4326</v>
       </c>
     </row>
     <row r="57">
@@ -5650,10 +8150,10 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>540.9817</v>
+        <v>312.7093</v>
       </c>
       <c r="C57" t="n">
-        <v>537.4880000000001</v>
+        <v>309.533</v>
       </c>
     </row>
     <row r="58">
@@ -5661,10 +8161,10 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>540.9817</v>
+        <v>312.7093</v>
       </c>
       <c r="C58" t="n">
-        <v>534.9918</v>
+        <v>308.5017</v>
       </c>
     </row>
     <row r="59">
@@ -5672,10 +8172,10 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>540.9817</v>
+        <v>312.7093</v>
       </c>
       <c r="C59" t="n">
-        <v>536.684</v>
+        <v>309.2914</v>
       </c>
     </row>
     <row r="60">
@@ -5683,10 +8183,10 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>540.9817</v>
+        <v>312.7093</v>
       </c>
       <c r="C60" t="n">
-        <v>537.0845</v>
+        <v>309.6218</v>
       </c>
     </row>
     <row r="61">
@@ -5694,10 +8194,120 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>540.9817</v>
+        <v>312.7093</v>
       </c>
       <c r="C61" t="n">
-        <v>536.4351</v>
+        <v>309.9991</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="n">
+        <v>312.7093</v>
+      </c>
+      <c r="C62" t="n">
+        <v>309.6803</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="n">
+        <v>312.7093</v>
+      </c>
+      <c r="C63" t="n">
+        <v>310.8127</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="n">
+        <v>312.7093</v>
+      </c>
+      <c r="C64" t="n">
+        <v>309.8784</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="n">
+        <v>312.7093</v>
+      </c>
+      <c r="C65" t="n">
+        <v>309.9135</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="n">
+        <v>312.7093</v>
+      </c>
+      <c r="C66" t="n">
+        <v>309.1106</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="n">
+        <v>312.7093</v>
+      </c>
+      <c r="C67" t="n">
+        <v>310.0765</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="n">
+        <v>312.7093</v>
+      </c>
+      <c r="C68" t="n">
+        <v>309.9</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="n">
+        <v>312.7093</v>
+      </c>
+      <c r="C69" t="n">
+        <v>310.5508</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="n">
+        <v>312.7093</v>
+      </c>
+      <c r="C70" t="n">
+        <v>309.6347</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="n">
+        <v>312.7093</v>
+      </c>
+      <c r="C71" t="n">
+        <v>308.5832</v>
       </c>
     </row>
   </sheetData>

--- a/data/exports/optimization/lotto_genetic_optimizer_results.xlsx
+++ b/data/exports/optimization/lotto_genetic_optimizer_results.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W94"/>
+  <dimension ref="A1:W90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -557,7 +557,7 @@
         <v>56</v>
       </c>
       <c r="H2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I2" t="n">
         <v>206</v>
@@ -596,7 +596,7 @@
         <v>14.519</v>
       </c>
       <c r="U2" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -632,7 +632,7 @@
         <v>56</v>
       </c>
       <c r="H3" t="n">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="I3" t="n">
         <v>206</v>
@@ -671,7 +671,7 @@
         <v>14.519</v>
       </c>
       <c r="U3" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -680,7 +680,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
         <v>56</v>
       </c>
       <c r="H4" t="n">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="I4" t="n">
         <v>206</v>
@@ -746,7 +746,7 @@
         <v>14.519</v>
       </c>
       <c r="U4" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -755,7 +755,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -782,7 +782,7 @@
         <v>56</v>
       </c>
       <c r="H5" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="I5" t="n">
         <v>206</v>
@@ -821,7 +821,7 @@
         <v>14.519</v>
       </c>
       <c r="U5" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
         <v>56</v>
       </c>
       <c r="H6" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="I6" t="n">
         <v>206</v>
@@ -896,7 +896,7 @@
         <v>14.519</v>
       </c>
       <c r="U6" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -932,7 +932,7 @@
         <v>56</v>
       </c>
       <c r="H7" t="n">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="I7" t="n">
         <v>206</v>
@@ -971,7 +971,7 @@
         <v>14.519</v>
       </c>
       <c r="U7" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
         <v>56</v>
       </c>
       <c r="H8" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="I8" t="n">
         <v>206</v>
@@ -1046,7 +1046,7 @@
         <v>14.519</v>
       </c>
       <c r="U8" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
         <v>56</v>
       </c>
       <c r="H9" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="I9" t="n">
         <v>206</v>
@@ -1121,7 +1121,7 @@
         <v>14.519</v>
       </c>
       <c r="U9" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
         <v>56</v>
       </c>
       <c r="H10" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="I10" t="n">
         <v>206</v>
@@ -1196,7 +1196,7 @@
         <v>14.519</v>
       </c>
       <c r="U10" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
         <v>56</v>
       </c>
       <c r="H11" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="I11" t="n">
         <v>206</v>
@@ -1271,7 +1271,7 @@
         <v>14.519</v>
       </c>
       <c r="U11" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
         <v>56</v>
       </c>
       <c r="H12" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="I12" t="n">
         <v>206</v>
@@ -1346,7 +1346,7 @@
         <v>14.519</v>
       </c>
       <c r="U12" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -1382,7 +1382,7 @@
         <v>56</v>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
+        <v>54</v>
       </c>
       <c r="I13" t="n">
         <v>206</v>
@@ -1421,7 +1421,7 @@
         <v>14.519</v>
       </c>
       <c r="U13" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -1457,7 +1457,7 @@
         <v>56</v>
       </c>
       <c r="H14" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="I14" t="n">
         <v>206</v>
@@ -1496,7 +1496,7 @@
         <v>14.519</v>
       </c>
       <c r="U14" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
         <v>56</v>
       </c>
       <c r="H15" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I15" t="n">
         <v>206</v>
@@ -1571,7 +1571,7 @@
         <v>14.519</v>
       </c>
       <c r="U15" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -1607,7 +1607,7 @@
         <v>56</v>
       </c>
       <c r="H16" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I16" t="n">
         <v>206</v>
@@ -1646,7 +1646,7 @@
         <v>14.519</v>
       </c>
       <c r="U16" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
         <v>56</v>
       </c>
       <c r="H17" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="I17" t="n">
         <v>206</v>
@@ -1721,7 +1721,7 @@
         <v>14.519</v>
       </c>
       <c r="U17" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -1757,7 +1757,7 @@
         <v>56</v>
       </c>
       <c r="H18" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="I18" t="n">
         <v>206</v>
@@ -1796,7 +1796,7 @@
         <v>14.519</v>
       </c>
       <c r="U18" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -1832,7 +1832,7 @@
         <v>56</v>
       </c>
       <c r="H19" t="n">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="I19" t="n">
         <v>206</v>
@@ -1871,7 +1871,7 @@
         <v>14.519</v>
       </c>
       <c r="U19" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -1907,7 +1907,7 @@
         <v>56</v>
       </c>
       <c r="H20" t="n">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="I20" t="n">
         <v>206</v>
@@ -1946,7 +1946,7 @@
         <v>14.519</v>
       </c>
       <c r="U20" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
         <v>56</v>
       </c>
       <c r="H21" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I21" t="n">
         <v>206</v>
@@ -2021,7 +2021,7 @@
         <v>14.519</v>
       </c>
       <c r="U21" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2057,7 @@
         <v>56</v>
       </c>
       <c r="H22" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I22" t="n">
         <v>206</v>
@@ -2096,7 +2096,7 @@
         <v>14.519</v>
       </c>
       <c r="U22" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2132,7 @@
         <v>56</v>
       </c>
       <c r="H23" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="I23" t="n">
         <v>206</v>
@@ -2171,7 +2171,7 @@
         <v>14.519</v>
       </c>
       <c r="U23" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -2207,7 +2207,7 @@
         <v>56</v>
       </c>
       <c r="H24" t="n">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="I24" t="n">
         <v>206</v>
@@ -2246,7 +2246,7 @@
         <v>14.519</v>
       </c>
       <c r="U24" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2282,7 @@
         <v>56</v>
       </c>
       <c r="H25" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="I25" t="n">
         <v>206</v>
@@ -2321,7 +2321,7 @@
         <v>14.519</v>
       </c>
       <c r="U25" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -2357,7 +2357,7 @@
         <v>56</v>
       </c>
       <c r="H26" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="I26" t="n">
         <v>206</v>
@@ -2396,7 +2396,7 @@
         <v>14.519</v>
       </c>
       <c r="U26" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -2432,7 +2432,7 @@
         <v>56</v>
       </c>
       <c r="H27" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="I27" t="n">
         <v>206</v>
@@ -2471,7 +2471,7 @@
         <v>14.519</v>
       </c>
       <c r="U27" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -2507,7 +2507,7 @@
         <v>56</v>
       </c>
       <c r="H28" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="I28" t="n">
         <v>206</v>
@@ -2546,7 +2546,7 @@
         <v>14.519</v>
       </c>
       <c r="U28" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -2582,7 +2582,7 @@
         <v>56</v>
       </c>
       <c r="H29" t="n">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="I29" t="n">
         <v>206</v>
@@ -2621,7 +2621,7 @@
         <v>14.519</v>
       </c>
       <c r="U29" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -2657,7 +2657,7 @@
         <v>56</v>
       </c>
       <c r="H30" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="I30" t="n">
         <v>206</v>
@@ -2696,7 +2696,7 @@
         <v>14.519</v>
       </c>
       <c r="U30" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -2732,7 +2732,7 @@
         <v>56</v>
       </c>
       <c r="H31" t="n">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="I31" t="n">
         <v>206</v>
@@ -2771,7 +2771,7 @@
         <v>14.519</v>
       </c>
       <c r="U31" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -2807,7 +2807,7 @@
         <v>56</v>
       </c>
       <c r="H32" t="n">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="I32" t="n">
         <v>206</v>
@@ -2846,7 +2846,7 @@
         <v>14.519</v>
       </c>
       <c r="U32" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -2867,7 +2867,7 @@
         <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D33" t="n">
         <v>44</v>
@@ -2882,10 +2882,10 @@
         <v>56</v>
       </c>
       <c r="H33" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="I33" t="n">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="J33" t="n">
         <v>4</v>
@@ -2915,13 +2915,13 @@
         <v>2</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T33" t="n">
-        <v>14.519</v>
+        <v>15.5563</v>
       </c>
       <c r="U33" t="n">
-        <v>312.7093</v>
+        <v>311.5865</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -2954,13 +2954,13 @@
         <v>52</v>
       </c>
       <c r="G34" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H34" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="I34" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="J34" t="n">
         <v>4</v>
@@ -2993,10 +2993,10 @@
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>14.519</v>
+        <v>14.3471</v>
       </c>
       <c r="U34" t="n">
-        <v>312.7093</v>
+        <v>311.2282</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -3014,7 +3014,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C35" t="n">
         <v>4</v>
@@ -3032,10 +3032,10 @@
         <v>56</v>
       </c>
       <c r="H35" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I35" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="J35" t="n">
         <v>4</v>
@@ -3065,13 +3065,13 @@
         <v>2</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T35" t="n">
-        <v>14.519</v>
+        <v>14.7594</v>
       </c>
       <c r="U35" t="n">
-        <v>312.7093</v>
+        <v>309.6526</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -3089,10 +3089,10 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D36" t="n">
         <v>44</v>
@@ -3107,10 +3107,10 @@
         <v>56</v>
       </c>
       <c r="H36" t="n">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="I36" t="n">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="J36" t="n">
         <v>4</v>
@@ -3140,13 +3140,13 @@
         <v>2</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T36" t="n">
-        <v>14.519</v>
+        <v>14.3611</v>
       </c>
       <c r="U36" t="n">
-        <v>312.7093</v>
+        <v>308.2697</v>
       </c>
       <c r="V36" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -3167,7 +3167,7 @@
         <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D37" t="n">
         <v>44</v>
@@ -3182,10 +3182,10 @@
         <v>56</v>
       </c>
       <c r="H37" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I37" t="n">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="J37" t="n">
         <v>4</v>
@@ -3194,10 +3194,10 @@
         <v>2</v>
       </c>
       <c r="L37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N37" t="n">
         <v>2</v>
@@ -3215,13 +3215,13 @@
         <v>2</v>
       </c>
       <c r="S37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>15.5563</v>
+        <v>12.1161</v>
       </c>
       <c r="U37" t="n">
-        <v>311.4115</v>
+        <v>306.4188</v>
       </c>
       <c r="V37" t="inlineStr">
         <is>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -3239,16 +3239,16 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C38" t="n">
         <v>4</v>
       </c>
       <c r="D38" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="E38" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F38" t="n">
         <v>52</v>
@@ -3257,10 +3257,10 @@
         <v>56</v>
       </c>
       <c r="H38" t="n">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="I38" t="n">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="J38" t="n">
         <v>4</v>
@@ -3281,22 +3281,22 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R38" t="n">
         <v>2</v>
       </c>
       <c r="S38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>14.7594</v>
+        <v>12.1161</v>
       </c>
       <c r="U38" t="n">
-        <v>309.3026</v>
+        <v>306.2401</v>
       </c>
       <c r="V38" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -3320,28 +3320,28 @@
         <v>4</v>
       </c>
       <c r="D39" t="n">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="E39" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F39" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G39" t="n">
         <v>56</v>
       </c>
       <c r="H39" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I39" t="n">
-        <v>200</v>
+        <v>172</v>
       </c>
       <c r="J39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L39" t="n">
         <v>2</v>
@@ -3353,25 +3353,25 @@
         <v>2</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P39" t="n">
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>14.6014</v>
+        <v>9.444599999999999</v>
       </c>
       <c r="U39" t="n">
-        <v>307.9001</v>
+        <v>305.7248</v>
       </c>
       <c r="V39" t="inlineStr">
         <is>
@@ -3380,7 +3380,7 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -3395,22 +3395,22 @@
         <v>4</v>
       </c>
       <c r="D40" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E40" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F40" t="n">
+        <v>51</v>
+      </c>
+      <c r="G40" t="n">
         <v>52</v>
       </c>
-      <c r="G40" t="n">
-        <v>56</v>
-      </c>
       <c r="H40" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I40" t="n">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="J40" t="n">
         <v>4</v>
@@ -3419,10 +3419,10 @@
         <v>2</v>
       </c>
       <c r="L40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M40" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N40" t="n">
         <v>2</v>
@@ -3431,22 +3431,22 @@
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R40" t="n">
         <v>2</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T40" t="n">
-        <v>12.1161</v>
+        <v>14.9586</v>
       </c>
       <c r="U40" t="n">
-        <v>306.0651</v>
+        <v>305.6291</v>
       </c>
       <c r="V40" t="inlineStr">
         <is>
@@ -3455,7 +3455,7 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -3476,16 +3476,16 @@
         <v>49</v>
       </c>
       <c r="F41" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G41" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="H41" t="n">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="I41" t="n">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="J41" t="n">
         <v>4</v>
@@ -3494,10 +3494,10 @@
         <v>2</v>
       </c>
       <c r="L41" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N41" t="n">
         <v>2</v>
@@ -3515,13 +3515,13 @@
         <v>2</v>
       </c>
       <c r="S41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>14.9586</v>
+        <v>14.4028</v>
       </c>
       <c r="U41" t="n">
-        <v>305.6291</v>
+        <v>305.6165</v>
       </c>
       <c r="V41" t="inlineStr">
         <is>
@@ -3530,7 +3530,7 @@
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -3542,7 +3542,7 @@
         <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D42" t="n">
         <v>44</v>
@@ -3551,16 +3551,16 @@
         <v>49</v>
       </c>
       <c r="F42" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G42" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I42" t="n">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="J42" t="n">
         <v>4</v>
@@ -3569,16 +3569,16 @@
         <v>2</v>
       </c>
       <c r="L42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P42" t="n">
         <v>1</v>
@@ -3593,10 +3593,10 @@
         <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>14.4028</v>
+        <v>9.2736</v>
       </c>
       <c r="U42" t="n">
-        <v>305.2665</v>
+        <v>305.0511</v>
       </c>
       <c r="V42" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
         <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D43" t="n">
         <v>44</v>
@@ -3632,10 +3632,10 @@
         <v>56</v>
       </c>
       <c r="H43" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="I43" t="n">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="J43" t="n">
         <v>4</v>
@@ -3644,10 +3644,10 @@
         <v>2</v>
       </c>
       <c r="L43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M43" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N43" t="n">
         <v>1</v>
@@ -3671,7 +3671,7 @@
         <v>9.2736</v>
       </c>
       <c r="U43" t="n">
-        <v>304.4511</v>
+        <v>304.4774</v>
       </c>
       <c r="V43" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -3692,13 +3692,13 @@
         <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="D44" t="n">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="E44" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F44" t="n">
         <v>52</v>
@@ -3707,16 +3707,16 @@
         <v>56</v>
       </c>
       <c r="H44" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="I44" t="n">
-        <v>230</v>
+        <v>174</v>
       </c>
       <c r="J44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L44" t="n">
         <v>2</v>
@@ -3725,7 +3725,7 @@
         <v>4</v>
       </c>
       <c r="N44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O44" t="n">
         <v>1</v>
@@ -3734,7 +3734,7 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R44" t="n">
         <v>2</v>
@@ -3743,10 +3743,10 @@
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>9.2736</v>
+        <v>8.7407</v>
       </c>
       <c r="U44" t="n">
-        <v>304.3024</v>
+        <v>303.2302</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -3764,10 +3764,10 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D45" t="n">
         <v>44</v>
@@ -3776,16 +3776,16 @@
         <v>49</v>
       </c>
       <c r="F45" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G45" t="n">
         <v>56</v>
       </c>
       <c r="H45" t="n">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="I45" t="n">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="J45" t="n">
         <v>4</v>
@@ -3794,10 +3794,10 @@
         <v>2</v>
       </c>
       <c r="L45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M45" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N45" t="n">
         <v>2</v>
@@ -3818,10 +3818,10 @@
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>13.8362</v>
+        <v>14.5465</v>
       </c>
       <c r="U45" t="n">
-        <v>303.4038</v>
+        <v>303.1439</v>
       </c>
       <c r="V45" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -3845,7 +3845,7 @@
         <v>4</v>
       </c>
       <c r="D46" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E46" t="n">
         <v>44</v>
@@ -3857,10 +3857,10 @@
         <v>56</v>
       </c>
       <c r="H46" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="I46" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J46" t="n">
         <v>4</v>
@@ -3869,10 +3869,10 @@
         <v>2</v>
       </c>
       <c r="L46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M46" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N46" t="n">
         <v>2</v>
@@ -3893,10 +3893,10 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>13.0843</v>
+        <v>12.5698</v>
       </c>
       <c r="U46" t="n">
-        <v>303.3799</v>
+        <v>303.0992</v>
       </c>
       <c r="V46" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -3920,13 +3920,13 @@
         <v>4</v>
       </c>
       <c r="D47" t="n">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="E47" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F47" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="G47" t="n">
         <v>56</v>
@@ -3935,22 +3935,22 @@
         <v>13</v>
       </c>
       <c r="I47" t="n">
-        <v>208</v>
+        <v>161</v>
       </c>
       <c r="J47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -3959,19 +3959,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>14.5465</v>
+        <v>13.0843</v>
       </c>
       <c r="U47" t="n">
-        <v>302.9689</v>
+        <v>302.6849</v>
       </c>
       <c r="V47" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -3995,58 +3995,58 @@
         <v>4</v>
       </c>
       <c r="D48" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="E48" t="n">
         <v>44</v>
       </c>
       <c r="F48" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G48" t="n">
         <v>56</v>
       </c>
       <c r="H48" t="n">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="I48" t="n">
-        <v>194</v>
+        <v>163</v>
       </c>
       <c r="J48" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M48" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q48" t="n">
         <v>2</v>
       </c>
       <c r="R48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>12.5698</v>
+        <v>13.6528</v>
       </c>
       <c r="U48" t="n">
-        <v>302.9242</v>
+        <v>301.8892</v>
       </c>
       <c r="V48" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -4070,22 +4070,22 @@
         <v>4</v>
       </c>
       <c r="D49" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E49" t="n">
         <v>44</v>
       </c>
       <c r="F49" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G49" t="n">
         <v>56</v>
       </c>
       <c r="H49" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="I49" t="n">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="J49" t="n">
         <v>3</v>
@@ -4094,16 +4094,16 @@
         <v>3</v>
       </c>
       <c r="L49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M49" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
         <v>1</v>
@@ -4112,16 +4112,16 @@
         <v>2</v>
       </c>
       <c r="R49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>8.7407</v>
+        <v>12.0665</v>
       </c>
       <c r="U49" t="n">
-        <v>302.6302</v>
+        <v>301.7762</v>
       </c>
       <c r="V49" t="inlineStr">
         <is>
@@ -4130,7 +4130,7 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -4145,7 +4145,7 @@
         <v>4</v>
       </c>
       <c r="D50" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E50" t="n">
         <v>44</v>
@@ -4157,10 +4157,10 @@
         <v>56</v>
       </c>
       <c r="H50" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I50" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="J50" t="n">
         <v>3</v>
@@ -4193,10 +4193,10 @@
         <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>13.0843</v>
+        <v>12.0665</v>
       </c>
       <c r="U50" t="n">
-        <v>302.5099</v>
+        <v>301.7762</v>
       </c>
       <c r="V50" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -4220,37 +4220,37 @@
         <v>4</v>
       </c>
       <c r="D51" t="n">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="E51" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F51" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G51" t="n">
         <v>56</v>
       </c>
       <c r="H51" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="I51" t="n">
-        <v>163</v>
+        <v>209</v>
       </c>
       <c r="J51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M51" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -4259,19 +4259,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R51" t="n">
         <v>2</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T51" t="n">
-        <v>13.6528</v>
+        <v>14.6014</v>
       </c>
       <c r="U51" t="n">
-        <v>301.7142</v>
+        <v>301.0976</v>
       </c>
       <c r="V51" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -4292,31 +4292,31 @@
         <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D52" t="n">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="E52" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F52" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G52" t="n">
         <v>56</v>
       </c>
       <c r="H52" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="I52" t="n">
-        <v>163</v>
+        <v>227</v>
       </c>
       <c r="J52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L52" t="n">
         <v>3</v>
@@ -4325,28 +4325,28 @@
         <v>3</v>
       </c>
       <c r="N52" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P52" t="n">
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>12.0665</v>
+        <v>8.7407</v>
       </c>
       <c r="U52" t="n">
-        <v>301.6012</v>
+        <v>300.9952</v>
       </c>
       <c r="V52" t="inlineStr">
         <is>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -4370,37 +4370,37 @@
         <v>4</v>
       </c>
       <c r="D53" t="n">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="E53" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F53" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G53" t="n">
         <v>56</v>
       </c>
       <c r="H53" t="n">
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="I53" t="n">
-        <v>163</v>
+        <v>196</v>
       </c>
       <c r="J53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -4409,19 +4409,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>12.0665</v>
+        <v>10.5262</v>
       </c>
       <c r="U53" t="n">
-        <v>301.6012</v>
+        <v>300.6382</v>
       </c>
       <c r="V53" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -4442,13 +4442,13 @@
         <v>1</v>
       </c>
       <c r="C54" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="D54" t="n">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="E54" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F54" t="n">
         <v>52</v>
@@ -4457,25 +4457,25 @@
         <v>56</v>
       </c>
       <c r="H54" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I54" t="n">
-        <v>227</v>
+        <v>180</v>
       </c>
       <c r="J54" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O54" t="n">
         <v>1</v>
@@ -4484,7 +4484,7 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R54" t="n">
         <v>2</v>
@@ -4493,10 +4493,10 @@
         <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>8.7407</v>
+        <v>7.5631</v>
       </c>
       <c r="U54" t="n">
-        <v>300.8202</v>
+        <v>299.5028</v>
       </c>
       <c r="V54" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -4520,22 +4520,22 @@
         <v>4</v>
       </c>
       <c r="D55" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E55" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F55" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="G55" t="n">
         <v>56</v>
       </c>
       <c r="H55" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="I55" t="n">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="J55" t="n">
         <v>4</v>
@@ -4544,10 +4544,10 @@
         <v>2</v>
       </c>
       <c r="L55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M55" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N55" t="n">
         <v>2</v>
@@ -4556,22 +4556,22 @@
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>14.6014</v>
+        <v>11.5758</v>
       </c>
       <c r="U55" t="n">
-        <v>300.7476</v>
+        <v>299.4586</v>
       </c>
       <c r="V55" t="inlineStr">
         <is>
@@ -4580,7 +4580,7 @@
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -4595,58 +4595,58 @@
         <v>4</v>
       </c>
       <c r="D56" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="E56" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F56" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G56" t="n">
         <v>56</v>
       </c>
       <c r="H56" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="I56" t="n">
-        <v>196</v>
+        <v>171</v>
       </c>
       <c r="J56" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M56" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N56" t="n">
         <v>2</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P56" t="n">
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>10.5262</v>
+        <v>8.671799999999999</v>
       </c>
       <c r="U56" t="n">
-        <v>300.4632</v>
+        <v>298.6785</v>
       </c>
       <c r="V56" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -4670,22 +4670,22 @@
         <v>4</v>
       </c>
       <c r="D57" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E57" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F57" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G57" t="n">
         <v>56</v>
       </c>
       <c r="H57" t="n">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="I57" t="n">
-        <v>170</v>
+        <v>188</v>
       </c>
       <c r="J57" t="n">
         <v>3</v>
@@ -4706,22 +4706,22 @@
         <v>1</v>
       </c>
       <c r="P57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>9.011100000000001</v>
+        <v>9.402100000000001</v>
       </c>
       <c r="U57" t="n">
-        <v>300.1598</v>
+        <v>298.0247</v>
       </c>
       <c r="V57" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -4745,10 +4745,10 @@
         <v>4</v>
       </c>
       <c r="D58" t="n">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="E58" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F58" t="n">
         <v>52</v>
@@ -4757,16 +4757,16 @@
         <v>56</v>
       </c>
       <c r="H58" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I58" t="n">
-        <v>180</v>
+        <v>210</v>
       </c>
       <c r="J58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L58" t="n">
         <v>2</v>
@@ -4778,25 +4778,25 @@
         <v>2</v>
       </c>
       <c r="O58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R58" t="n">
         <v>2</v>
       </c>
       <c r="S58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T58" t="n">
-        <v>7.5631</v>
+        <v>16.5288</v>
       </c>
       <c r="U58" t="n">
-        <v>299.3278</v>
+        <v>297.583</v>
       </c>
       <c r="V58" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -4820,58 +4820,58 @@
         <v>4</v>
       </c>
       <c r="D59" t="n">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="E59" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F59" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G59" t="n">
         <v>56</v>
       </c>
       <c r="H59" t="n">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="I59" t="n">
-        <v>171</v>
+        <v>210</v>
       </c>
       <c r="J59" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K59" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L59" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M59" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N59" t="n">
         <v>2</v>
       </c>
       <c r="O59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T59" t="n">
-        <v>8.671799999999999</v>
+        <v>16.5288</v>
       </c>
       <c r="U59" t="n">
-        <v>298.0785</v>
+        <v>297.583</v>
       </c>
       <c r="V59" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -4889,13 +4889,13 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C60" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D60" t="n">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="E60" t="n">
         <v>49</v>
@@ -4907,31 +4907,31 @@
         <v>56</v>
       </c>
       <c r="H60" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="I60" t="n">
-        <v>188</v>
+        <v>223</v>
       </c>
       <c r="J60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M60" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O60" t="n">
         <v>1</v>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q60" t="n">
         <v>3</v>
@@ -4943,10 +4943,10 @@
         <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>9.402100000000001</v>
+        <v>8.7316</v>
       </c>
       <c r="U60" t="n">
-        <v>297.8497</v>
+        <v>296.9221</v>
       </c>
       <c r="V60" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -4964,13 +4964,13 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C61" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D61" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E61" t="n">
         <v>49</v>
@@ -4982,10 +4982,10 @@
         <v>56</v>
       </c>
       <c r="H61" t="n">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="I61" t="n">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="J61" t="n">
         <v>4</v>
@@ -4994,10 +4994,10 @@
         <v>2</v>
       </c>
       <c r="L61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N61" t="n">
         <v>2</v>
@@ -5006,22 +5006,22 @@
         <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R61" t="n">
         <v>2</v>
       </c>
       <c r="S61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>16.5288</v>
+        <v>10.9289</v>
       </c>
       <c r="U61" t="n">
-        <v>297.408</v>
+        <v>295.6196</v>
       </c>
       <c r="V61" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -5039,13 +5039,13 @@
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C62" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="D62" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E62" t="n">
         <v>49</v>
@@ -5057,16 +5057,16 @@
         <v>56</v>
       </c>
       <c r="H62" t="n">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="I62" t="n">
-        <v>210</v>
+        <v>246</v>
       </c>
       <c r="J62" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L62" t="n">
         <v>2</v>
@@ -5075,28 +5075,28 @@
         <v>4</v>
       </c>
       <c r="N62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q62" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R62" t="n">
         <v>2</v>
       </c>
       <c r="S62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>16.5288</v>
+        <v>13.3207</v>
       </c>
       <c r="U62" t="n">
-        <v>297.408</v>
+        <v>295.6053</v>
       </c>
       <c r="V62" t="inlineStr">
         <is>
@@ -5105,7 +5105,7 @@
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -5117,7 +5117,7 @@
         <v>4</v>
       </c>
       <c r="C63" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D63" t="n">
         <v>44</v>
@@ -5132,10 +5132,10 @@
         <v>56</v>
       </c>
       <c r="H63" t="n">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="I63" t="n">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="J63" t="n">
         <v>4</v>
@@ -5168,10 +5168,10 @@
         <v>0</v>
       </c>
       <c r="T63" t="n">
-        <v>8.7316</v>
+        <v>8.2608</v>
       </c>
       <c r="U63" t="n">
-        <v>295.5471</v>
+        <v>295.4439</v>
       </c>
       <c r="V63" t="inlineStr">
         <is>
@@ -5180,7 +5180,7 @@
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -5189,64 +5189,64 @@
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C64" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D64" t="n">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="E64" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F64" t="n">
+        <v>49</v>
+      </c>
+      <c r="G64" t="n">
         <v>52</v>
       </c>
-      <c r="G64" t="n">
-        <v>56</v>
-      </c>
       <c r="H64" t="n">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="I64" t="n">
-        <v>217</v>
+        <v>167</v>
       </c>
       <c r="J64" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L64" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M64" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N64" t="n">
         <v>2</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P64" t="n">
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
       </c>
       <c r="T64" t="n">
-        <v>10.9289</v>
+        <v>9.1739</v>
       </c>
       <c r="U64" t="n">
-        <v>295.4446</v>
+        <v>294.6644</v>
       </c>
       <c r="V64" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -5264,43 +5264,43 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C65" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="D65" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="E65" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F65" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G65" t="n">
         <v>56</v>
       </c>
       <c r="H65" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I65" t="n">
-        <v>246</v>
+        <v>187</v>
       </c>
       <c r="J65" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M65" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -5309,19 +5309,19 @@
         <v>2</v>
       </c>
       <c r="Q65" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
       </c>
       <c r="T65" t="n">
-        <v>13.3207</v>
+        <v>9.380800000000001</v>
       </c>
       <c r="U65" t="n">
-        <v>295.4303</v>
+        <v>294.4913</v>
       </c>
       <c r="V65" t="inlineStr">
         <is>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -5339,28 +5339,28 @@
         <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C66" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="D66" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="E66" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F66" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G66" t="n">
         <v>56</v>
       </c>
       <c r="H66" t="n">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="I66" t="n">
-        <v>225</v>
+        <v>187</v>
       </c>
       <c r="J66" t="n">
         <v>4</v>
@@ -5369,34 +5369,34 @@
         <v>2</v>
       </c>
       <c r="L66" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M66" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
       </c>
       <c r="T66" t="n">
-        <v>8.2608</v>
+        <v>9.380800000000001</v>
       </c>
       <c r="U66" t="n">
-        <v>295.2689</v>
+        <v>294.4913</v>
       </c>
       <c r="V66" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -5420,7 +5420,7 @@
         <v>4</v>
       </c>
       <c r="D67" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E67" t="n">
         <v>44</v>
@@ -5429,13 +5429,13 @@
         <v>49</v>
       </c>
       <c r="G67" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="H67" t="n">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="I67" t="n">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="J67" t="n">
         <v>3</v>
@@ -5468,10 +5468,10 @@
         <v>0</v>
       </c>
       <c r="T67" t="n">
-        <v>9.1739</v>
+        <v>8.099399999999999</v>
       </c>
       <c r="U67" t="n">
-        <v>294.3144</v>
+        <v>294.3758</v>
       </c>
       <c r="V67" t="inlineStr">
         <is>
@@ -5480,7 +5480,7 @@
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -5489,43 +5489,43 @@
         <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C68" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="D68" t="n">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="E68" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F68" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G68" t="n">
         <v>56</v>
       </c>
       <c r="H68" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="I68" t="n">
-        <v>173</v>
+        <v>227</v>
       </c>
       <c r="J68" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K68" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L68" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M68" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O68" t="n">
         <v>1</v>
@@ -5534,19 +5534,19 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
       </c>
       <c r="T68" t="n">
-        <v>8.099399999999999</v>
+        <v>7.9649</v>
       </c>
       <c r="U68" t="n">
-        <v>294.2008</v>
+        <v>294.2468</v>
       </c>
       <c r="V68" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
       </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -5570,7 +5570,7 @@
         <v>4</v>
       </c>
       <c r="D69" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="E69" t="n">
         <v>44</v>
@@ -5582,31 +5582,31 @@
         <v>56</v>
       </c>
       <c r="H69" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="I69" t="n">
-        <v>187</v>
+        <v>168</v>
       </c>
       <c r="J69" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L69" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M69" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q69" t="n">
         <v>2</v>
@@ -5618,10 +5618,10 @@
         <v>0</v>
       </c>
       <c r="T69" t="n">
-        <v>9.380800000000001</v>
+        <v>9.7775</v>
       </c>
       <c r="U69" t="n">
-        <v>294.1413</v>
+        <v>294.0146</v>
       </c>
       <c r="V69" t="inlineStr">
         <is>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="W69" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -5645,7 +5645,7 @@
         <v>4</v>
       </c>
       <c r="D70" t="n">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="E70" t="n">
         <v>44</v>
@@ -5657,31 +5657,31 @@
         <v>56</v>
       </c>
       <c r="H70" t="n">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="I70" t="n">
-        <v>187</v>
+        <v>168</v>
       </c>
       <c r="J70" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q70" t="n">
         <v>2</v>
@@ -5693,10 +5693,10 @@
         <v>0</v>
       </c>
       <c r="T70" t="n">
-        <v>9.380800000000001</v>
+        <v>9.7775</v>
       </c>
       <c r="U70" t="n">
-        <v>294.1413</v>
+        <v>294.0146</v>
       </c>
       <c r="V70" t="inlineStr">
         <is>
@@ -5705,7 +5705,7 @@
       </c>
       <c r="W70" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -5714,64 +5714,64 @@
         <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C71" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="D71" t="n">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="E71" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F71" t="n">
+        <v>49</v>
+      </c>
+      <c r="G71" t="n">
         <v>52</v>
       </c>
-      <c r="G71" t="n">
-        <v>56</v>
-      </c>
       <c r="H71" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I71" t="n">
-        <v>227</v>
+        <v>162</v>
       </c>
       <c r="J71" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K71" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M71" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N71" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P71" t="n">
         <v>1</v>
       </c>
       <c r="Q71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
       </c>
       <c r="T71" t="n">
-        <v>7.9649</v>
+        <v>11.0526</v>
       </c>
       <c r="U71" t="n">
-        <v>294.0718</v>
+        <v>293.341</v>
       </c>
       <c r="V71" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
       </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -5795,7 +5795,7 @@
         <v>4</v>
       </c>
       <c r="D72" t="n">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="E72" t="n">
         <v>44</v>
@@ -5804,34 +5804,34 @@
         <v>49</v>
       </c>
       <c r="G72" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="H72" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="I72" t="n">
-        <v>168</v>
+        <v>187</v>
       </c>
       <c r="J72" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K72" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M72" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N72" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
       </c>
       <c r="P72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q72" t="n">
         <v>2</v>
@@ -5843,10 +5843,10 @@
         <v>0</v>
       </c>
       <c r="T72" t="n">
-        <v>9.7775</v>
+        <v>11.4961</v>
       </c>
       <c r="U72" t="n">
-        <v>293.8396</v>
+        <v>292.794</v>
       </c>
       <c r="V72" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
       </c>
       <c r="W72" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -5867,31 +5867,31 @@
         <v>1</v>
       </c>
       <c r="C73" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="D73" t="n">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="E73" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F73" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G73" t="n">
         <v>56</v>
       </c>
       <c r="H73" t="n">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="I73" t="n">
-        <v>168</v>
+        <v>248</v>
       </c>
       <c r="J73" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K73" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L73" t="n">
         <v>2</v>
@@ -5900,7 +5900,7 @@
         <v>4</v>
       </c>
       <c r="N73" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -5909,19 +5909,19 @@
         <v>1</v>
       </c>
       <c r="Q73" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
       </c>
       <c r="T73" t="n">
-        <v>9.7775</v>
+        <v>16.0125</v>
       </c>
       <c r="U73" t="n">
-        <v>293.8396</v>
+        <v>291.5912</v>
       </c>
       <c r="V73" t="inlineStr">
         <is>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="W73" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -5942,31 +5942,31 @@
         <v>1</v>
       </c>
       <c r="C74" t="n">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="D74" t="n">
+        <v>44</v>
+      </c>
+      <c r="E74" t="n">
+        <v>49</v>
+      </c>
+      <c r="F74" t="n">
+        <v>52</v>
+      </c>
+      <c r="G74" t="n">
+        <v>56</v>
+      </c>
+      <c r="H74" t="n">
         <v>12</v>
       </c>
-      <c r="E74" t="n">
-        <v>44</v>
-      </c>
-      <c r="F74" t="n">
-        <v>49</v>
-      </c>
-      <c r="G74" t="n">
-        <v>52</v>
-      </c>
-      <c r="H74" t="n">
-        <v>51</v>
-      </c>
       <c r="I74" t="n">
-        <v>162</v>
+        <v>238</v>
       </c>
       <c r="J74" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K74" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L74" t="n">
         <v>2</v>
@@ -5975,28 +5975,28 @@
         <v>4</v>
       </c>
       <c r="N74" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
       </c>
       <c r="P74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
       </c>
       <c r="T74" t="n">
-        <v>11.0526</v>
+        <v>12.1161</v>
       </c>
       <c r="U74" t="n">
-        <v>293.341</v>
+        <v>291.5738</v>
       </c>
       <c r="V74" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
       </c>
       <c r="W74" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
         <v>4</v>
       </c>
       <c r="D75" t="n">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="E75" t="n">
         <v>44</v>
@@ -6032,16 +6032,16 @@
         <v>52</v>
       </c>
       <c r="H75" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="I75" t="n">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="J75" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L75" t="n">
         <v>3</v>
@@ -6053,10 +6053,10 @@
         <v>2</v>
       </c>
       <c r="O75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q75" t="n">
         <v>2</v>
@@ -6068,10 +6068,10 @@
         <v>0</v>
       </c>
       <c r="T75" t="n">
-        <v>11.4961</v>
+        <v>8.2559</v>
       </c>
       <c r="U75" t="n">
-        <v>292.794</v>
+        <v>291.439</v>
       </c>
       <c r="V75" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
       </c>
       <c r="W75" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -6089,13 +6089,13 @@
         <v>75</v>
       </c>
       <c r="B76" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C76" t="n">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="D76" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E76" t="n">
         <v>49</v>
@@ -6107,25 +6107,25 @@
         <v>56</v>
       </c>
       <c r="H76" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I76" t="n">
-        <v>219</v>
+        <v>249</v>
       </c>
       <c r="J76" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L76" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M76" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -6134,7 +6134,7 @@
         <v>1</v>
       </c>
       <c r="Q76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R76" t="n">
         <v>2</v>
@@ -6143,10 +6143,10 @@
         <v>0</v>
       </c>
       <c r="T76" t="n">
-        <v>10.0916</v>
+        <v>16.0125</v>
       </c>
       <c r="U76" t="n">
-        <v>292.1677</v>
+        <v>290.8537</v>
       </c>
       <c r="V76" t="inlineStr">
         <is>
@@ -6155,7 +6155,7 @@
       </c>
       <c r="W76" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -6170,22 +6170,22 @@
         <v>4</v>
       </c>
       <c r="D77" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E77" t="n">
         <v>44</v>
       </c>
       <c r="F77" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G77" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="H77" t="n">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="I77" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J77" t="n">
         <v>3</v>
@@ -6194,16 +6194,16 @@
         <v>3</v>
       </c>
       <c r="L77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M77" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P77" t="n">
         <v>1</v>
@@ -6212,16 +6212,16 @@
         <v>2</v>
       </c>
       <c r="R77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
       </c>
       <c r="T77" t="n">
-        <v>8.133900000000001</v>
+        <v>9.838699999999999</v>
       </c>
       <c r="U77" t="n">
-        <v>291.8924</v>
+        <v>290.8521</v>
       </c>
       <c r="V77" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="W77" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -6242,13 +6242,13 @@
         <v>1</v>
       </c>
       <c r="C78" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="D78" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="E78" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F78" t="n">
         <v>52</v>
@@ -6257,25 +6257,25 @@
         <v>56</v>
       </c>
       <c r="H78" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="I78" t="n">
-        <v>238</v>
+        <v>191</v>
       </c>
       <c r="J78" t="n">
+        <v>4</v>
+      </c>
+      <c r="K78" t="n">
+        <v>2</v>
+      </c>
+      <c r="L78" t="n">
+        <v>1</v>
+      </c>
+      <c r="M78" t="n">
         <v>5</v>
       </c>
-      <c r="K78" t="n">
-        <v>1</v>
-      </c>
-      <c r="L78" t="n">
-        <v>2</v>
-      </c>
-      <c r="M78" t="n">
-        <v>4</v>
-      </c>
       <c r="N78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -6284,7 +6284,7 @@
         <v>2</v>
       </c>
       <c r="Q78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R78" t="n">
         <v>2</v>
@@ -6293,10 +6293,10 @@
         <v>0</v>
       </c>
       <c r="T78" t="n">
-        <v>12.1161</v>
+        <v>9.838699999999999</v>
       </c>
       <c r="U78" t="n">
-        <v>291.3988</v>
+        <v>290.1346</v>
       </c>
       <c r="V78" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
       </c>
       <c r="W78" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -6317,31 +6317,31 @@
         <v>1</v>
       </c>
       <c r="C79" t="n">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="D79" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E79" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F79" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G79" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H79" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="I79" t="n">
-        <v>248</v>
+        <v>214</v>
       </c>
       <c r="J79" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L79" t="n">
         <v>2</v>
@@ -6350,7 +6350,7 @@
         <v>4</v>
       </c>
       <c r="N79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -6359,19 +6359,19 @@
         <v>1</v>
       </c>
       <c r="Q79" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T79" t="n">
-        <v>16.0125</v>
+        <v>14.5794</v>
       </c>
       <c r="U79" t="n">
-        <v>291.2412</v>
+        <v>289.9799</v>
       </c>
       <c r="V79" t="inlineStr">
         <is>
@@ -6380,7 +6380,7 @@
       </c>
       <c r="W79" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -6395,7 +6395,7 @@
         <v>4</v>
       </c>
       <c r="D80" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E80" t="n">
         <v>44</v>
@@ -6407,16 +6407,16 @@
         <v>52</v>
       </c>
       <c r="H80" t="n">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="I80" t="n">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="J80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K80" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L80" t="n">
         <v>2</v>
@@ -6428,10 +6428,10 @@
         <v>2</v>
       </c>
       <c r="O80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q80" t="n">
         <v>2</v>
@@ -6443,10 +6443,10 @@
         <v>0</v>
       </c>
       <c r="T80" t="n">
-        <v>8.133900000000001</v>
+        <v>9.4953</v>
       </c>
       <c r="U80" t="n">
-        <v>290.8461</v>
+        <v>289.8392</v>
       </c>
       <c r="V80" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
       </c>
       <c r="W80" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -6470,37 +6470,37 @@
         <v>4</v>
       </c>
       <c r="D81" t="n">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="E81" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F81" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G81" t="n">
         <v>56</v>
       </c>
       <c r="H81" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="I81" t="n">
-        <v>171</v>
+        <v>212</v>
       </c>
       <c r="J81" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K81" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M81" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N81" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -6509,19 +6509,19 @@
         <v>1</v>
       </c>
       <c r="Q81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T81" t="n">
-        <v>9.838699999999999</v>
+        <v>14.6833</v>
       </c>
       <c r="U81" t="n">
-        <v>290.6771</v>
+        <v>289.3458</v>
       </c>
       <c r="V81" t="inlineStr">
         <is>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="W81" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -6539,13 +6539,13 @@
         <v>81</v>
       </c>
       <c r="B82" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C82" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="D82" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E82" t="n">
         <v>49</v>
@@ -6557,10 +6557,10 @@
         <v>56</v>
       </c>
       <c r="H82" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I82" t="n">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="J82" t="n">
         <v>5</v>
@@ -6569,10 +6569,10 @@
         <v>1</v>
       </c>
       <c r="L82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N82" t="n">
         <v>1</v>
@@ -6581,10 +6581,10 @@
         <v>0</v>
       </c>
       <c r="P82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q82" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R82" t="n">
         <v>2</v>
@@ -6593,10 +6593,10 @@
         <v>0</v>
       </c>
       <c r="T82" t="n">
-        <v>16.0125</v>
+        <v>11.3772</v>
       </c>
       <c r="U82" t="n">
-        <v>290.5037</v>
+        <v>289.2773</v>
       </c>
       <c r="V82" t="inlineStr">
         <is>
@@ -6605,7 +6605,7 @@
       </c>
       <c r="W82" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -6617,13 +6617,13 @@
         <v>1</v>
       </c>
       <c r="C83" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="D83" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="E83" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F83" t="n">
         <v>52</v>
@@ -6632,25 +6632,25 @@
         <v>56</v>
       </c>
       <c r="H83" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="I83" t="n">
-        <v>191</v>
+        <v>236</v>
       </c>
       <c r="J83" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M83" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -6659,7 +6659,7 @@
         <v>2</v>
       </c>
       <c r="Q83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R83" t="n">
         <v>2</v>
@@ -6668,10 +6668,10 @@
         <v>0</v>
       </c>
       <c r="T83" t="n">
-        <v>9.838699999999999</v>
+        <v>11.2606</v>
       </c>
       <c r="U83" t="n">
-        <v>289.9596</v>
+        <v>288.062</v>
       </c>
       <c r="V83" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
       </c>
       <c r="W83" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -6692,31 +6692,31 @@
         <v>1</v>
       </c>
       <c r="C84" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="D84" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="E84" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F84" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G84" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="H84" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="I84" t="n">
-        <v>182</v>
+        <v>236</v>
       </c>
       <c r="J84" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L84" t="n">
         <v>2</v>
@@ -6725,7 +6725,7 @@
         <v>4</v>
       </c>
       <c r="N84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -6734,19 +6734,19 @@
         <v>2</v>
       </c>
       <c r="Q84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
       </c>
       <c r="T84" t="n">
-        <v>9.4953</v>
+        <v>11.2606</v>
       </c>
       <c r="U84" t="n">
-        <v>289.8392</v>
+        <v>288.062</v>
       </c>
       <c r="V84" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="W84" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -6770,22 +6770,22 @@
         <v>4</v>
       </c>
       <c r="D85" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E85" t="n">
+        <v>51</v>
+      </c>
+      <c r="F85" t="n">
         <v>52</v>
       </c>
-      <c r="F85" t="n">
-        <v>56</v>
-      </c>
       <c r="G85" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H85" t="n">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="I85" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="J85" t="n">
         <v>4</v>
@@ -6794,10 +6794,10 @@
         <v>2</v>
       </c>
       <c r="L85" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M85" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N85" t="n">
         <v>2</v>
@@ -6806,10 +6806,10 @@
         <v>0</v>
       </c>
       <c r="P85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R85" t="n">
         <v>3</v>
@@ -6818,10 +6818,10 @@
         <v>1</v>
       </c>
       <c r="T85" t="n">
-        <v>14.5794</v>
+        <v>17.0294</v>
       </c>
       <c r="U85" t="n">
-        <v>289.8049</v>
+        <v>287.3985</v>
       </c>
       <c r="V85" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="W85" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -6842,7 +6842,7 @@
         <v>4</v>
       </c>
       <c r="C86" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D86" t="n">
         <v>44</v>
@@ -6857,10 +6857,10 @@
         <v>56</v>
       </c>
       <c r="H86" t="n">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="I86" t="n">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="J86" t="n">
         <v>5</v>
@@ -6893,10 +6893,10 @@
         <v>0</v>
       </c>
       <c r="T86" t="n">
-        <v>11.3772</v>
+        <v>10.4995</v>
       </c>
       <c r="U86" t="n">
-        <v>289.1023</v>
+        <v>286.7899</v>
       </c>
       <c r="V86" t="inlineStr">
         <is>
@@ -6905,7 +6905,7 @@
       </c>
       <c r="W86" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -6920,22 +6920,22 @@
         <v>4</v>
       </c>
       <c r="D87" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="E87" t="n">
+        <v>44</v>
+      </c>
+      <c r="F87" t="n">
+        <v>49</v>
+      </c>
+      <c r="G87" t="n">
         <v>52</v>
       </c>
-      <c r="F87" t="n">
-        <v>55</v>
-      </c>
-      <c r="G87" t="n">
-        <v>56</v>
-      </c>
       <c r="H87" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="I87" t="n">
-        <v>212</v>
+        <v>180</v>
       </c>
       <c r="J87" t="n">
         <v>4</v>
@@ -6956,22 +6956,22 @@
         <v>0</v>
       </c>
       <c r="P87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q87" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R87" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T87" t="n">
-        <v>14.6833</v>
+        <v>8.885899999999999</v>
       </c>
       <c r="U87" t="n">
-        <v>288.9958</v>
+        <v>286.7231</v>
       </c>
       <c r="V87" t="inlineStr">
         <is>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="W87" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -6992,7 +6992,7 @@
         <v>1</v>
       </c>
       <c r="C88" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D88" t="n">
         <v>44</v>
@@ -7007,10 +7007,10 @@
         <v>56</v>
       </c>
       <c r="H88" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I88" t="n">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="J88" t="n">
         <v>5</v>
@@ -7019,10 +7019,10 @@
         <v>1</v>
       </c>
       <c r="L88" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M88" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N88" t="n">
         <v>1</v>
@@ -7043,10 +7043,10 @@
         <v>0</v>
       </c>
       <c r="T88" t="n">
-        <v>11.2606</v>
+        <v>10.139</v>
       </c>
       <c r="U88" t="n">
-        <v>287.887</v>
+        <v>285.5593</v>
       </c>
       <c r="V88" t="inlineStr">
         <is>
@@ -7055,7 +7055,7 @@
       </c>
       <c r="W88" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -7067,13 +7067,13 @@
         <v>1</v>
       </c>
       <c r="C89" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="D89" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="E89" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F89" t="n">
         <v>52</v>
@@ -7082,16 +7082,16 @@
         <v>56</v>
       </c>
       <c r="H89" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="I89" t="n">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="J89" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L89" t="n">
         <v>3</v>
@@ -7100,28 +7100,28 @@
         <v>3</v>
       </c>
       <c r="N89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q89" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R89" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T89" t="n">
-        <v>17.0294</v>
+        <v>10.139</v>
       </c>
       <c r="U89" t="n">
-        <v>287.2235</v>
+        <v>285.5593</v>
       </c>
       <c r="V89" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
       </c>
       <c r="W89" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -7145,22 +7145,22 @@
         <v>4</v>
       </c>
       <c r="D90" t="n">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="E90" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F90" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="G90" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="H90" t="n">
-        <v>7</v>
+        <v>54</v>
       </c>
       <c r="I90" t="n">
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="J90" t="n">
         <v>4</v>
@@ -7181,22 +7181,22 @@
         <v>0</v>
       </c>
       <c r="P90" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R90" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
       </c>
       <c r="T90" t="n">
-        <v>8.885899999999999</v>
+        <v>16.8119</v>
       </c>
       <c r="U90" t="n">
-        <v>286.7231</v>
+        <v>282.8796</v>
       </c>
       <c r="V90" t="inlineStr">
         <is>
@@ -7205,307 +7205,7 @@
       </c>
       <c r="W90" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:19</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="n">
-        <v>90</v>
-      </c>
-      <c r="B91" t="n">
-        <v>4</v>
-      </c>
-      <c r="C91" t="n">
-        <v>35</v>
-      </c>
-      <c r="D91" t="n">
-        <v>44</v>
-      </c>
-      <c r="E91" t="n">
-        <v>49</v>
-      </c>
-      <c r="F91" t="n">
-        <v>52</v>
-      </c>
-      <c r="G91" t="n">
-        <v>56</v>
-      </c>
-      <c r="H91" t="n">
-        <v>8</v>
-      </c>
-      <c r="I91" t="n">
-        <v>240</v>
-      </c>
-      <c r="J91" t="n">
-        <v>5</v>
-      </c>
-      <c r="K91" t="n">
-        <v>1</v>
-      </c>
-      <c r="L91" t="n">
-        <v>2</v>
-      </c>
-      <c r="M91" t="n">
-        <v>4</v>
-      </c>
-      <c r="N91" t="n">
-        <v>1</v>
-      </c>
-      <c r="O91" t="n">
-        <v>0</v>
-      </c>
-      <c r="P91" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q91" t="n">
-        <v>3</v>
-      </c>
-      <c r="R91" t="n">
-        <v>2</v>
-      </c>
-      <c r="S91" t="n">
-        <v>0</v>
-      </c>
-      <c r="T91" t="n">
-        <v>10.4995</v>
-      </c>
-      <c r="U91" t="n">
-        <v>286.3649</v>
-      </c>
-      <c r="V91" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v2_range_balanced</t>
-        </is>
-      </c>
-      <c r="W91" t="inlineStr">
-        <is>
-          <t>2026-05-28 08:54:19</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="n">
-        <v>91</v>
-      </c>
-      <c r="B92" t="n">
-        <v>1</v>
-      </c>
-      <c r="C92" t="n">
-        <v>31</v>
-      </c>
-      <c r="D92" t="n">
-        <v>44</v>
-      </c>
-      <c r="E92" t="n">
-        <v>49</v>
-      </c>
-      <c r="F92" t="n">
-        <v>52</v>
-      </c>
-      <c r="G92" t="n">
-        <v>56</v>
-      </c>
-      <c r="H92" t="n">
-        <v>7</v>
-      </c>
-      <c r="I92" t="n">
-        <v>233</v>
-      </c>
-      <c r="J92" t="n">
-        <v>5</v>
-      </c>
-      <c r="K92" t="n">
-        <v>1</v>
-      </c>
-      <c r="L92" t="n">
-        <v>3</v>
-      </c>
-      <c r="M92" t="n">
-        <v>3</v>
-      </c>
-      <c r="N92" t="n">
-        <v>1</v>
-      </c>
-      <c r="O92" t="n">
-        <v>0</v>
-      </c>
-      <c r="P92" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q92" t="n">
-        <v>3</v>
-      </c>
-      <c r="R92" t="n">
-        <v>2</v>
-      </c>
-      <c r="S92" t="n">
-        <v>0</v>
-      </c>
-      <c r="T92" t="n">
-        <v>10.139</v>
-      </c>
-      <c r="U92" t="n">
-        <v>285.2093</v>
-      </c>
-      <c r="V92" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v2_range_balanced</t>
-        </is>
-      </c>
-      <c r="W92" t="inlineStr">
-        <is>
-          <t>2026-05-28 08:54:19</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="n">
-        <v>92</v>
-      </c>
-      <c r="B93" t="n">
-        <v>1</v>
-      </c>
-      <c r="C93" t="n">
-        <v>31</v>
-      </c>
-      <c r="D93" t="n">
-        <v>44</v>
-      </c>
-      <c r="E93" t="n">
-        <v>49</v>
-      </c>
-      <c r="F93" t="n">
-        <v>52</v>
-      </c>
-      <c r="G93" t="n">
-        <v>56</v>
-      </c>
-      <c r="H93" t="n">
-        <v>57</v>
-      </c>
-      <c r="I93" t="n">
-        <v>233</v>
-      </c>
-      <c r="J93" t="n">
-        <v>5</v>
-      </c>
-      <c r="K93" t="n">
-        <v>1</v>
-      </c>
-      <c r="L93" t="n">
-        <v>3</v>
-      </c>
-      <c r="M93" t="n">
-        <v>3</v>
-      </c>
-      <c r="N93" t="n">
-        <v>1</v>
-      </c>
-      <c r="O93" t="n">
-        <v>0</v>
-      </c>
-      <c r="P93" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q93" t="n">
-        <v>3</v>
-      </c>
-      <c r="R93" t="n">
-        <v>2</v>
-      </c>
-      <c r="S93" t="n">
-        <v>0</v>
-      </c>
-      <c r="T93" t="n">
-        <v>10.139</v>
-      </c>
-      <c r="U93" t="n">
-        <v>285.2093</v>
-      </c>
-      <c r="V93" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v2_range_balanced</t>
-        </is>
-      </c>
-      <c r="W93" t="inlineStr">
-        <is>
-          <t>2026-05-28 08:54:19</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="n">
-        <v>93</v>
-      </c>
-      <c r="B94" t="n">
-        <v>1</v>
-      </c>
-      <c r="C94" t="n">
-        <v>4</v>
-      </c>
-      <c r="D94" t="n">
-        <v>49</v>
-      </c>
-      <c r="E94" t="n">
-        <v>52</v>
-      </c>
-      <c r="F94" t="n">
-        <v>56</v>
-      </c>
-      <c r="G94" t="n">
-        <v>58</v>
-      </c>
-      <c r="H94" t="n">
-        <v>3</v>
-      </c>
-      <c r="I94" t="n">
-        <v>220</v>
-      </c>
-      <c r="J94" t="n">
-        <v>4</v>
-      </c>
-      <c r="K94" t="n">
-        <v>2</v>
-      </c>
-      <c r="L94" t="n">
-        <v>2</v>
-      </c>
-      <c r="M94" t="n">
-        <v>4</v>
-      </c>
-      <c r="N94" t="n">
-        <v>2</v>
-      </c>
-      <c r="O94" t="n">
-        <v>0</v>
-      </c>
-      <c r="P94" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q94" t="n">
-        <v>4</v>
-      </c>
-      <c r="R94" t="n">
-        <v>3</v>
-      </c>
-      <c r="S94" t="n">
-        <v>0</v>
-      </c>
-      <c r="T94" t="n">
-        <v>16.8119</v>
-      </c>
-      <c r="U94" t="n">
-        <v>282.5296</v>
-      </c>
-      <c r="V94" t="inlineStr">
-        <is>
-          <t>LottoGeneticOptimizer_v2_range_balanced</t>
-        </is>
-      </c>
-      <c r="W94" t="inlineStr">
-        <is>
-          <t>2026-05-28 08:54:19</t>
+          <t>2026-05-28 17:22:24</t>
         </is>
       </c>
     </row>
@@ -7545,10 +7245,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>298.1834</v>
+        <v>298.7682</v>
       </c>
       <c r="C2" t="n">
-        <v>256.2051</v>
+        <v>256.5812</v>
       </c>
     </row>
     <row r="3">
@@ -7556,10 +7256,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>302.4646</v>
+        <v>303.2516</v>
       </c>
       <c r="C3" t="n">
-        <v>276.7191</v>
+        <v>276.3396</v>
       </c>
     </row>
     <row r="4">
@@ -7567,10 +7267,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>306.3161</v>
+        <v>308.4631</v>
       </c>
       <c r="C4" t="n">
-        <v>280.3123</v>
+        <v>282.7505</v>
       </c>
     </row>
     <row r="5">
@@ -7578,10 +7278,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>309.2925</v>
+        <v>308.4631</v>
       </c>
       <c r="C5" t="n">
-        <v>286.1664</v>
+        <v>283.3171</v>
       </c>
     </row>
     <row r="6">
@@ -7589,10 +7289,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>310.3221</v>
+        <v>309.5215</v>
       </c>
       <c r="C6" t="n">
-        <v>288.7889</v>
+        <v>285.1784</v>
       </c>
     </row>
     <row r="7">
@@ -7600,10 +7300,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>310.7661</v>
+        <v>309.5215</v>
       </c>
       <c r="C7" t="n">
-        <v>289.557</v>
+        <v>283.3762</v>
       </c>
     </row>
     <row r="8">
@@ -7611,10 +7311,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>310.7661</v>
+        <v>309.5215</v>
       </c>
       <c r="C8" t="n">
-        <v>289.8532</v>
+        <v>291.1291</v>
       </c>
     </row>
     <row r="9">
@@ -7622,10 +7322,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>310.7661</v>
+        <v>310.3234</v>
       </c>
       <c r="C9" t="n">
-        <v>293.8831</v>
+        <v>294.7213</v>
       </c>
     </row>
     <row r="10">
@@ -7633,10 +7333,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>310.7661</v>
+        <v>310.3234</v>
       </c>
       <c r="C10" t="n">
-        <v>295.7263</v>
+        <v>294.9464</v>
       </c>
     </row>
     <row r="11">
@@ -7644,10 +7344,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>312.3839</v>
+        <v>310.3234</v>
       </c>
       <c r="C11" t="n">
-        <v>297.3298</v>
+        <v>296.4806</v>
       </c>
     </row>
     <row r="12">
@@ -7655,10 +7355,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>312.7093</v>
+        <v>311.0145</v>
       </c>
       <c r="C12" t="n">
-        <v>302.5974</v>
+        <v>297.5284</v>
       </c>
     </row>
     <row r="13">
@@ -7666,10 +7366,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>312.7093</v>
+        <v>311.0145</v>
       </c>
       <c r="C13" t="n">
-        <v>304.6619</v>
+        <v>296.4801</v>
       </c>
     </row>
     <row r="14">
@@ -7677,10 +7377,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>312.7093</v>
+        <v>311.0145</v>
       </c>
       <c r="C14" t="n">
-        <v>301.8013</v>
+        <v>298.326</v>
       </c>
     </row>
     <row r="15">
@@ -7688,10 +7388,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>312.7093</v>
+        <v>311.0145</v>
       </c>
       <c r="C15" t="n">
-        <v>298.98</v>
+        <v>304.4156</v>
       </c>
     </row>
     <row r="16">
@@ -7699,10 +7399,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>312.7093</v>
+        <v>311.0145</v>
       </c>
       <c r="C16" t="n">
-        <v>302.7916</v>
+        <v>304.0744</v>
       </c>
     </row>
     <row r="17">
@@ -7710,10 +7410,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>312.7093</v>
+        <v>311.1799</v>
       </c>
       <c r="C17" t="n">
-        <v>308.5304</v>
+        <v>307.057</v>
       </c>
     </row>
     <row r="18">
@@ -7721,10 +7421,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>312.7093</v>
+        <v>312.8651</v>
       </c>
       <c r="C18" t="n">
-        <v>309.2483</v>
+        <v>308.0654</v>
       </c>
     </row>
     <row r="19">
@@ -7732,10 +7432,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>312.7093</v>
+        <v>312.8651</v>
       </c>
       <c r="C19" t="n">
-        <v>310.2212</v>
+        <v>307.913</v>
       </c>
     </row>
     <row r="20">
@@ -7743,10 +7443,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>312.7093</v>
+        <v>312.8651</v>
       </c>
       <c r="C20" t="n">
-        <v>309.1595</v>
+        <v>307.104</v>
       </c>
     </row>
     <row r="21">
@@ -7754,10 +7454,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>312.7093</v>
+        <v>312.8651</v>
       </c>
       <c r="C21" t="n">
-        <v>310.043</v>
+        <v>305.2168</v>
       </c>
     </row>
     <row r="22">
@@ -7765,10 +7465,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>312.7093</v>
+        <v>312.8651</v>
       </c>
       <c r="C22" t="n">
-        <v>309.8011</v>
+        <v>305.2931</v>
       </c>
     </row>
     <row r="23">
@@ -7776,10 +7476,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>312.7093</v>
+        <v>312.8651</v>
       </c>
       <c r="C23" t="n">
-        <v>309.6977</v>
+        <v>310.1439</v>
       </c>
     </row>
     <row r="24">
@@ -7787,10 +7487,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>312.7093</v>
+        <v>312.8651</v>
       </c>
       <c r="C24" t="n">
-        <v>309.4656</v>
+        <v>309.6444</v>
       </c>
     </row>
     <row r="25">
@@ -7798,10 +7498,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>312.7093</v>
+        <v>312.8651</v>
       </c>
       <c r="C25" t="n">
-        <v>309.942</v>
+        <v>310.3984</v>
       </c>
     </row>
     <row r="26">
@@ -7809,10 +7509,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="C26" t="n">
-        <v>309.6856</v>
+        <v>310.1124</v>
       </c>
     </row>
     <row r="27">
@@ -7820,10 +7520,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="C27" t="n">
-        <v>309.3516</v>
+        <v>309.341</v>
       </c>
     </row>
     <row r="28">
@@ -7831,10 +7531,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="C28" t="n">
-        <v>309.154</v>
+        <v>309.6422</v>
       </c>
     </row>
     <row r="29">
@@ -7842,10 +7542,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="C29" t="n">
-        <v>310.0958</v>
+        <v>308.4499</v>
       </c>
     </row>
     <row r="30">
@@ -7853,10 +7553,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="C30" t="n">
-        <v>309.2065</v>
+        <v>304.5744</v>
       </c>
     </row>
     <row r="31">
@@ -7864,10 +7564,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="C31" t="n">
-        <v>309.1689</v>
+        <v>302.5618</v>
       </c>
     </row>
     <row r="32">
@@ -7875,10 +7575,10 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="C32" t="n">
-        <v>309.7652</v>
+        <v>309.896</v>
       </c>
     </row>
     <row r="33">
@@ -7886,10 +7586,10 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="C33" t="n">
-        <v>309.6731</v>
+        <v>310.0715</v>
       </c>
     </row>
     <row r="34">
@@ -7897,10 +7597,10 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="C34" t="n">
-        <v>309.866</v>
+        <v>309.8714</v>
       </c>
     </row>
     <row r="35">
@@ -7908,10 +7608,10 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="C35" t="n">
-        <v>309.7693</v>
+        <v>309.6265</v>
       </c>
     </row>
     <row r="36">
@@ -7919,10 +7619,10 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="C36" t="n">
-        <v>309.9437</v>
+        <v>310.4197</v>
       </c>
     </row>
     <row r="37">
@@ -7930,10 +7630,10 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="C37" t="n">
-        <v>309.6133</v>
+        <v>309.7169</v>
       </c>
     </row>
     <row r="38">
@@ -7941,10 +7641,10 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="C38" t="n">
-        <v>309.2757</v>
+        <v>309.6704</v>
       </c>
     </row>
     <row r="39">
@@ -7952,10 +7652,10 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="C39" t="n">
-        <v>309.6936</v>
+        <v>309.81</v>
       </c>
     </row>
     <row r="40">
@@ -7963,10 +7663,10 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="C40" t="n">
-        <v>309.7769</v>
+        <v>309.7601</v>
       </c>
     </row>
     <row r="41">
@@ -7974,10 +7674,10 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="C41" t="n">
-        <v>309.5322</v>
+        <v>309.7668</v>
       </c>
     </row>
     <row r="42">
@@ -7985,10 +7685,10 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="C42" t="n">
-        <v>309.2596</v>
+        <v>309.3494</v>
       </c>
     </row>
     <row r="43">
@@ -7996,10 +7696,10 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="C43" t="n">
-        <v>310.3059</v>
+        <v>310.6374</v>
       </c>
     </row>
     <row r="44">
@@ -8007,10 +7707,10 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="C44" t="n">
-        <v>309.8117</v>
+        <v>310.1348</v>
       </c>
     </row>
     <row r="45">
@@ -8018,10 +7718,10 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="C45" t="n">
-        <v>309.3354</v>
+        <v>309.4829</v>
       </c>
     </row>
     <row r="46">
@@ -8029,10 +7729,10 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="C46" t="n">
-        <v>309.4965</v>
+        <v>309.2018</v>
       </c>
     </row>
     <row r="47">
@@ -8040,10 +7740,10 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="C47" t="n">
-        <v>309.7624</v>
+        <v>310.3192</v>
       </c>
     </row>
     <row r="48">
@@ -8051,10 +7751,10 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="C48" t="n">
-        <v>308.8788</v>
+        <v>308.9455</v>
       </c>
     </row>
     <row r="49">
@@ -8062,10 +7762,10 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="C49" t="n">
-        <v>309.4504</v>
+        <v>309.8318</v>
       </c>
     </row>
     <row r="50">
@@ -8073,10 +7773,10 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="C50" t="n">
-        <v>309.6912</v>
+        <v>309.3085</v>
       </c>
     </row>
     <row r="51">
@@ -8084,10 +7784,10 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="C51" t="n">
-        <v>309.6809</v>
+        <v>310.1416</v>
       </c>
     </row>
     <row r="52">
@@ -8095,10 +7795,10 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="C52" t="n">
-        <v>309.8251</v>
+        <v>310.146</v>
       </c>
     </row>
     <row r="53">
@@ -8106,10 +7806,10 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="C53" t="n">
-        <v>309.7498</v>
+        <v>309.9987</v>
       </c>
     </row>
     <row r="54">
@@ -8117,10 +7817,10 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="C54" t="n">
-        <v>310.1662</v>
+        <v>310.0793</v>
       </c>
     </row>
     <row r="55">
@@ -8128,10 +7828,10 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="C55" t="n">
-        <v>309.3211</v>
+        <v>309.5489</v>
       </c>
     </row>
     <row r="56">
@@ -8139,10 +7839,10 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="C56" t="n">
-        <v>308.4326</v>
+        <v>308.9415</v>
       </c>
     </row>
     <row r="57">
@@ -8150,10 +7850,10 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="C57" t="n">
-        <v>309.533</v>
+        <v>309.2652</v>
       </c>
     </row>
     <row r="58">
@@ -8161,10 +7861,10 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="C58" t="n">
-        <v>308.5017</v>
+        <v>309.1153</v>
       </c>
     </row>
     <row r="59">
@@ -8172,10 +7872,10 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="C59" t="n">
-        <v>309.2914</v>
+        <v>309.149</v>
       </c>
     </row>
     <row r="60">
@@ -8183,10 +7883,10 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="C60" t="n">
-        <v>309.6218</v>
+        <v>310.11</v>
       </c>
     </row>
     <row r="61">
@@ -8194,10 +7894,10 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="C61" t="n">
-        <v>309.9991</v>
+        <v>309.9629</v>
       </c>
     </row>
     <row r="62">
@@ -8205,10 +7905,10 @@
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="C62" t="n">
-        <v>309.6803</v>
+        <v>310.076</v>
       </c>
     </row>
     <row r="63">
@@ -8216,10 +7916,10 @@
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="C63" t="n">
-        <v>310.8127</v>
+        <v>311.034</v>
       </c>
     </row>
     <row r="64">
@@ -8227,10 +7927,10 @@
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="C64" t="n">
-        <v>309.8784</v>
+        <v>309.7932</v>
       </c>
     </row>
     <row r="65">
@@ -8238,10 +7938,10 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="C65" t="n">
-        <v>309.9135</v>
+        <v>309.8972</v>
       </c>
     </row>
     <row r="66">
@@ -8249,10 +7949,10 @@
         <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="C66" t="n">
-        <v>309.1106</v>
+        <v>309.5313</v>
       </c>
     </row>
     <row r="67">
@@ -8260,10 +7960,10 @@
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="C67" t="n">
-        <v>310.0765</v>
+        <v>310.1651</v>
       </c>
     </row>
     <row r="68">
@@ -8271,10 +7971,10 @@
         <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="C68" t="n">
-        <v>309.9</v>
+        <v>310.4542</v>
       </c>
     </row>
     <row r="69">
@@ -8282,10 +7982,10 @@
         <v>68</v>
       </c>
       <c r="B69" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="C69" t="n">
-        <v>310.5508</v>
+        <v>310.503</v>
       </c>
     </row>
     <row r="70">
@@ -8293,10 +7993,10 @@
         <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="C70" t="n">
-        <v>309.6347</v>
+        <v>309.614</v>
       </c>
     </row>
     <row r="71">
@@ -8304,10 +8004,10 @@
         <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>312.7093</v>
+        <v>312.8843</v>
       </c>
       <c r="C71" t="n">
-        <v>308.5832</v>
+        <v>309.0906</v>
       </c>
     </row>
   </sheetData>

--- a/data/exports/optimization/lotto_genetic_optimizer_results.xlsx
+++ b/data/exports/optimization/lotto_genetic_optimizer_results.xlsx
@@ -605,7 +605,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -680,7 +680,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -905,7 +905,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -980,7 +980,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -1055,7 +1055,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -1205,7 +1205,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -1655,7 +1655,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -2180,7 +2180,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -2480,7 +2480,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -2555,7 +2555,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -2630,7 +2630,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -2705,7 +2705,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3005,7 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -3080,7 +3080,7 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -3230,7 +3230,7 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -3380,7 +3380,7 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -3455,7 +3455,7 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -3530,7 +3530,7 @@
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -3605,7 +3605,7 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -3680,7 +3680,7 @@
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -4130,7 +4130,7 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -4205,7 +4205,7 @@
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -4280,7 +4280,7 @@
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -4430,7 +4430,7 @@
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -4655,7 +4655,7 @@
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -4955,7 +4955,7 @@
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -5030,7 +5030,7 @@
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -5105,7 +5105,7 @@
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -5180,7 +5180,7 @@
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -5255,7 +5255,7 @@
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -5480,7 +5480,7 @@
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -5555,7 +5555,7 @@
       </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="W69" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -5705,7 +5705,7 @@
       </c>
       <c r="W70" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -5780,7 +5780,7 @@
       </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -5855,7 +5855,7 @@
       </c>
       <c r="W72" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="W73" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -6005,7 +6005,7 @@
       </c>
       <c r="W74" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -6080,7 +6080,7 @@
       </c>
       <c r="W75" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -6155,7 +6155,7 @@
       </c>
       <c r="W76" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="W77" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -6305,7 +6305,7 @@
       </c>
       <c r="W78" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -6380,7 +6380,7 @@
       </c>
       <c r="W79" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
       </c>
       <c r="W80" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -6530,7 +6530,7 @@
       </c>
       <c r="W81" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -6605,7 +6605,7 @@
       </c>
       <c r="W82" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -6680,7 +6680,7 @@
       </c>
       <c r="W83" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="W84" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="W85" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -6905,7 +6905,7 @@
       </c>
       <c r="W86" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
       </c>
       <c r="W87" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -7055,7 +7055,7 @@
       </c>
       <c r="W88" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -7130,7 +7130,7 @@
       </c>
       <c r="W89" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
@@ -7205,7 +7205,7 @@
       </c>
       <c r="W90" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:24</t>
+          <t>2026-05-28 19:49:46</t>
         </is>
       </c>
     </row>
